--- a/output/WC2026_predictions.xlsx
+++ b/output/WC2026_predictions.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>1.078 (uniform baseline 1.099; Elo-only 1.102)</t>
+          <t>1.095 (uniform baseline 1.099; Elo-only 1.124)</t>
         </is>
       </c>
     </row>
@@ -630,11 +630,11 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0.171155</v>
+        <v>0.17706</v>
       </c>
     </row>
     <row r="16">
@@ -643,11 +643,11 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>0.15701</v>
+        <v>0.1749</v>
       </c>
     </row>
     <row r="17">
@@ -656,11 +656,11 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.063555</v>
+        <v>0.07605000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -669,11 +669,11 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>0.06339</v>
+        <v>0.06647</v>
       </c>
     </row>
     <row r="19">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.05633</v>
+        <v>0.06223</v>
       </c>
     </row>
     <row r="20">
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>0.047965</v>
+        <v>0.05174</v>
       </c>
     </row>
     <row r="21">
@@ -708,11 +708,11 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>0.042455</v>
+        <v>0.04257</v>
       </c>
     </row>
     <row r="22">
@@ -721,11 +721,11 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>0.040975</v>
+        <v>0.033405</v>
       </c>
     </row>
     <row r="23">
@@ -734,11 +734,11 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>0.04089</v>
+        <v>0.031385</v>
       </c>
     </row>
     <row r="24">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>0.032105</v>
+        <v>0.03057</v>
       </c>
     </row>
   </sheetData>
@@ -765,7 +765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:N73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -780,6 +780,8 @@
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -843,6 +845,16 @@
           <t>Most likely scores</t>
         </is>
       </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>utc_kickoff</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
+          <t>local_kickoff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -876,23 +888,33 @@
         </is>
       </c>
       <c r="G2" s="8" t="n">
-        <v>0.4592147612634202</v>
+        <v>0.4876960392091589</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>0.2715840634077214</v>
+        <v>0.2694833227713974</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>0.2692011753288583</v>
+        <v>0.2428206380194437</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>1.499590200948142</v>
+        <v>1.521409138103637</v>
       </c>
       <c r="K2" s="9" t="n">
-        <v>1.091777777516905</v>
+        <v>0.9996626600231008</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
-          <t>1-1 (12.9%); 1-0 (10.6%); 2-1 (9.2%)</t>
+          <t>1-1 (12.8%); 1-0 (11.6%); 2-0 (9.3%)</t>
+        </is>
+      </c>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-12T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="inlineStr">
+        <is>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -928,23 +950,33 @@
         </is>
       </c>
       <c r="G3" s="11" t="n">
-        <v>0.7156012196883277</v>
+        <v>0.744921129844757</v>
       </c>
       <c r="H3" s="11" t="n">
-        <v>0.1935398477428961</v>
+        <v>0.1765639301739367</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>0.0908589325687762</v>
+        <v>0.07851493998130619</v>
       </c>
       <c r="J3" s="12" t="n">
-        <v>2.09254064970481</v>
+        <v>2.211939582509757</v>
       </c>
       <c r="K3" s="12" t="n">
-        <v>0.6085592078908805</v>
+        <v>0.5792024685504795</v>
       </c>
       <c r="L3" s="10" t="inlineStr">
         <is>
-          <t>2-0 (14.7%); 1-0 (13.6%); 3-0 (10.3%)</t>
+          <t>2-0 (15.0%); 1-0 (13.2%); 3-0 (11.1%)</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-11T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
     </row>
@@ -980,23 +1012,33 @@
         </is>
       </c>
       <c r="G4" s="8" t="n">
-        <v>0.7028790550306057</v>
+        <v>0.6993451491181814</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>0.1990425254025776</v>
+        <v>0.1979410164725726</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.09807841956681659</v>
+        <v>0.1027138344092458</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>2.06172919644596</v>
+        <v>2.074840893112762</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.6356443527980747</v>
+        <v>0.6621660805310114</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
-          <t>2-0 (14.3%); 1-0 (13.4%); 3-0 (9.8%)</t>
+          <t>2-0 (13.9%); 1-0 (13.0%); 3-0 (9.6%)</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-12T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
     </row>
@@ -1032,23 +1074,33 @@
         </is>
       </c>
       <c r="G5" s="11" t="n">
-        <v>0.3797773895679021</v>
+        <v>0.4622413077525104</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>0.2842289348479077</v>
+        <v>0.2796371077850134</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.3359936755841902</v>
+        <v>0.258121584462476</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>1.294025178255663</v>
+        <v>1.423105868596251</v>
       </c>
       <c r="K5" s="12" t="n">
-        <v>1.20219090369758</v>
+        <v>0.997383226954411</v>
       </c>
       <c r="L5" s="10" t="inlineStr">
         <is>
-          <t>1-1 (13.5%); 1-0 (9.9%); 0-1 (9.2%)</t>
+          <t>1-1 (13.2%); 1-0 (12.0%); 0-0 (9.5%)</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-13T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
     </row>
@@ -1084,23 +1136,33 @@
         </is>
       </c>
       <c r="G6" s="8" t="n">
-        <v>0.0822519948599419</v>
+        <v>0.1013060261674676</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>0.1626511137570359</v>
+        <v>0.1822866853453601</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.7550968913830221</v>
+        <v>0.7164072884871721</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.6986506929550766</v>
+        <v>0.7343915063721975</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>2.449899468912457</v>
+        <v>2.263968589711184</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>0-2 (12.9%); 0-3 (10.5%); 0-1 (10.1%)</t>
+          <t>0-2 (12.8%); 0-1 (10.9%); 0-3 (9.6%)</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-13T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
     </row>
@@ -1136,23 +1198,33 @@
         </is>
       </c>
       <c r="G7" s="11" t="n">
-        <v>0.3684003416877194</v>
+        <v>0.4053038268770442</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>0.3050823393266319</v>
+        <v>0.3011974735679947</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.3265173189856487</v>
+        <v>0.293498699554961</v>
       </c>
       <c r="J7" s="12" t="n">
-        <v>1.146852720017848</v>
+        <v>1.214480742114214</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>1.063462025438086</v>
+        <v>0.991608182870979</v>
       </c>
       <c r="L7" s="10" t="inlineStr">
         <is>
-          <t>1-1 (14.1%); 1-0 (11.8%); 0-0 (11.7%)</t>
+          <t>1-1 (13.9%); 1-0 (12.7%); 0-0 (11.7%)</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-13T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
     </row>
@@ -1188,23 +1260,33 @@
         </is>
       </c>
       <c r="G8" s="8" t="n">
-        <v>0.267881772389743</v>
+        <v>0.2307026435224526</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>0.2649614833442328</v>
+        <v>0.2586846044715399</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.4671567442660241</v>
+        <v>0.5106127520060075</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>1.127734381462095</v>
+        <v>1.014946258625834</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>1.562871006947737</v>
+        <v>1.625934878338498</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
-          <t>1-1 (12.6%); 0-1 (9.9%); 1-2 (9.3%)</t>
+          <t>1-1 (12.3%); 0-1 (11.0%); 1-2 (9.6%)</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-14T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>21:00</t>
         </is>
       </c>
     </row>
@@ -1240,23 +1322,33 @@
         </is>
       </c>
       <c r="G9" s="11" t="n">
-        <v>0.3548917719186636</v>
+        <v>0.4239028196431248</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0.2884189159186217</v>
+        <v>0.2834696067357887</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.3566893121627147</v>
+        <v>0.2926275736210864</v>
       </c>
       <c r="J9" s="12" t="n">
-        <v>1.217987453254279</v>
+        <v>1.353655175443633</v>
       </c>
       <c r="K9" s="12" t="n">
-        <v>1.22171920361828</v>
+        <v>1.080492255253987</v>
       </c>
       <c r="L9" s="10" t="inlineStr">
         <is>
-          <t>1-1 (13.7%); 0-1 (9.9%); 1-0 (9.9%)</t>
+          <t>1-1 (13.4%); 1-0 (11.3%); 0-0 (9.4%)</t>
+        </is>
+      </c>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-14T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
     </row>
@@ -1292,23 +1384,33 @@
         </is>
       </c>
       <c r="G10" s="8" t="n">
-        <v>0.7620157288539494</v>
+        <v>0.78221633669059</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>0.1593497080251923</v>
+        <v>0.1495377361180388</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0.0786345631208582</v>
+        <v>0.0682459271913711</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>2.473215084955043</v>
+        <v>2.51833738615422</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.6840441680679673</v>
+        <v>0.6262094533102728</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
-          <t>2-0 (13.0%); 3-0 (10.7%); 1-0 (10.1%)</t>
+          <t>2-0 (13.7%); 3-0 (11.5%); 1-0 (10.5%)</t>
+        </is>
+      </c>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-14T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
     </row>
@@ -1344,23 +1446,33 @@
         </is>
       </c>
       <c r="G11" s="11" t="n">
-        <v>0.2154067890218401</v>
+        <v>0.2009729216289915</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>0.3168698449124252</v>
+        <v>0.2942195629541478</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.4677233660657346</v>
+        <v>0.5048075154168605</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>0.7236695921904245</v>
+        <v>0.7443436856247659</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>1.203646709697187</v>
+        <v>1.345359272540166</v>
       </c>
       <c r="L11" s="10" t="inlineStr">
         <is>
-          <t>0-1 (16.8%); 0-0 (15.3%); 1-1 (13.4%)</t>
+          <t>0-1 (16.1%); 1-1 (13.0%); 0-0 (13.0%)</t>
+        </is>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-14T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
     </row>
@@ -1396,23 +1508,33 @@
         </is>
       </c>
       <c r="G12" s="8" t="n">
-        <v>0.3313246683882499</v>
+        <v>0.3523107119521086</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>0.2875295141302028</v>
+        <v>0.2849318661598131</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.3811458174815471</v>
+        <v>0.3627574218880782</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1.17103514095675</v>
+        <v>1.219747738157318</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1.274623130450717</v>
+        <v>1.241518399337046</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
-          <t>1-1 (13.7%); 0-1 (10.3%); 1-0 (9.4%)</t>
+          <t>1-1 (13.5%); 0-1 (10.0%); 1-0 (9.8%)</t>
+        </is>
+      </c>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-14T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
     </row>
@@ -1448,23 +1570,33 @@
         </is>
       </c>
       <c r="G13" s="11" t="n">
-        <v>0.3661622422812985</v>
+        <v>0.3751228653339352</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>0.2840288329753262</v>
+        <v>0.2903524140386735</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.3498089247433753</v>
+        <v>0.3345247206273913</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>1.269174815070143</v>
+        <v>1.231087304005712</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>1.234838964846302</v>
+        <v>1.147690201916116</v>
       </c>
       <c r="L13" s="10" t="inlineStr">
         <is>
-          <t>1-1 (13.5%); 1-0 (9.7%); 0-1 (9.4%)</t>
+          <t>1-1 (13.7%); 1-0 (10.8%); 0-1 (10.0%)</t>
+        </is>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-15T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -1500,23 +1632,33 @@
         </is>
       </c>
       <c r="G14" s="8" t="n">
-        <v>0.4804688210937872</v>
+        <v>0.4989500542283396</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>0.2868828037750159</v>
+        <v>0.2800377108664868</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0.2326483751311968</v>
+        <v>0.2210122349051734</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1.398193494651612</v>
+        <v>1.44281950541194</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.8915933812868306</v>
+        <v>0.8703823251453218</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
-          <t>1-0 (13.5%); 1-1 (13.3%); 0-0 (10.8%)</t>
+          <t>1-0 (13.7%); 1-1 (13.0%); 0-0 (10.5%)</t>
+        </is>
+      </c>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-15T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
     </row>
@@ -1552,23 +1694,33 @@
         </is>
       </c>
       <c r="G15" s="11" t="n">
-        <v>0.5339582190788172</v>
+        <v>0.5305552137951132</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>0.2588596954155595</v>
+        <v>0.2621884848997083</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.2071820855056234</v>
+        <v>0.2072563013051784</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>1.642279672698685</v>
+        <v>1.595322215797708</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>0.932733406770975</v>
+        <v>0.9029549677376748</v>
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>1-1 (12.3%); 1-0 (11.9%); 2-0 (10.3%)</t>
+          <t>1-0 (12.5%); 1-1 (12.4%); 2-0 (10.5%)</t>
+        </is>
+      </c>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-16T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
     </row>
@@ -1604,23 +1756,33 @@
         </is>
       </c>
       <c r="G16" s="8" t="n">
-        <v>0.8459887027678674</v>
+        <v>0.8646247173865226</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>0.1136002866400477</v>
+        <v>0.102220680108171</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0.0404110105920848</v>
+        <v>0.0331546025053062</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>2.839155093265337</v>
+        <v>2.919233272782865</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.5136095415403509</v>
+        <v>0.4615355558399334</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
-          <t>2-0 (14.1%); 3-0 (13.3%); 1-0 (9.6%)</t>
+          <t>2-0 (14.5%); 3-0 (14.1%); 4-0 (10.3%)</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-15T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
     </row>
@@ -1656,23 +1818,33 @@
         </is>
       </c>
       <c r="G17" s="11" t="n">
-        <v>0.1599073613392271</v>
+        <v>0.1396541131642705</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>0.2764414341318747</v>
+        <v>0.2521913252640903</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.5636512045288979</v>
+        <v>0.6081545615716389</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>0.66301832112282</v>
+        <v>0.6491375130072713</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>1.482108172569043</v>
+        <v>1.638394053110989</v>
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
-          <t>0-1 (16.7%); 0-2 (12.9%); 0-0 (12.3%)</t>
+          <t>0-1 (16.1%); 0-2 (13.6%); 1-1 (11.3%)</t>
+        </is>
+      </c>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-15T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="N17" s="10" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
     </row>
@@ -1708,23 +1880,33 @@
         </is>
       </c>
       <c r="G18" s="8" t="n">
-        <v>0.5977725992428286</v>
+        <v>0.6474891219800869</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>0.2512256824171425</v>
+        <v>0.2266236810991674</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>0.1510017183400288</v>
+        <v>0.1258871969207457</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>1.675127881352303</v>
+        <v>1.842617306223174</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.7171600715817109</v>
+        <v>0.6783967105094685</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
-          <t>1-0 (14.7%); 2-0 (12.8%); 1-1 (11.6%)</t>
+          <t>1-0 (14.3%); 2-0 (13.6%); 1-1 (10.5%)</t>
+        </is>
+      </c>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-17T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -1760,23 +1942,33 @@
         </is>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.4989566907628761</v>
+        <v>0.4969013122821983</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>0.2669290529347599</v>
+        <v>0.2688886225578228</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>0.234114256302364</v>
+        <v>0.2342100651599789</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>1.564796665664541</v>
+        <v>1.53081279295336</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>0.9955033817952756</v>
+        <v>0.971879472394593</v>
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>1-1 (12.7%); 1-0 (11.4%); 2-0 (9.5%)</t>
+          <t>1-1 (12.8%); 1-0 (11.9%); 2-0 (9.6%)</t>
+        </is>
+      </c>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-16T04:00:00Z</t>
+        </is>
+      </c>
+      <c r="N19" s="10" t="inlineStr">
+        <is>
+          <t>21:00</t>
         </is>
       </c>
     </row>
@@ -1812,23 +2004,33 @@
         </is>
       </c>
       <c r="G20" s="8" t="n">
-        <v>0.4877797125840392</v>
+        <v>0.5264630351441255</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>0.2734994853299927</v>
+        <v>0.2672904180724022</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>0.238720802085968</v>
+        <v>0.2062465467834721</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>1.504405040359404</v>
+        <v>1.55070271994623</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.977175274703612</v>
+        <v>0.8741234472023518</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
-          <t>1-1 (13.0%); 1-0 (11.9%); 2-0 (9.5%)</t>
+          <t>1-0 (13.1%); 1-1 (12.6%); 2-0 (10.6%)</t>
+        </is>
+      </c>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-16T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
     </row>
@@ -1864,23 +2066,33 @@
         </is>
       </c>
       <c r="G21" s="11" t="n">
-        <v>0.1629625289363759</v>
+        <v>0.1660485989641971</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>0.2488306239400371</v>
+        <v>0.2472668528074754</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>0.5882068471235867</v>
+        <v>0.5866845482283275</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>0.7845072168000257</v>
+        <v>0.7944485525319893</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>1.709467181953254</v>
+        <v>1.710363747668712</v>
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
-          <t>0-1 (13.5%); 0-2 (12.1%); 1-1 (11.7%)</t>
+          <t>0-1 (13.4%); 0-2 (11.9%); 1-1 (11.6%)</t>
+        </is>
+      </c>
+      <c r="M21" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-16T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="N21" s="10" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
     </row>
@@ -1916,23 +2128,33 @@
         </is>
       </c>
       <c r="G22" s="8" t="n">
-        <v>0.5736305791576619</v>
+        <v>0.6233267881935012</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>0.2647870555796083</v>
+        <v>0.2404473180352465</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>0.1615823652627294</v>
+        <v>0.1362258937712521</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>1.57191327120108</v>
+        <v>1.73383421559122</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.7118076808524076</v>
+        <v>0.6769048667841173</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>1-0 (15.4%); 2-0 (12.6%); 1-1 (12.0%)</t>
+          <t>1-0 (15.1%); 2-0 (13.5%); 1-1 (11.0%)</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-17T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
     </row>
@@ -1968,23 +2190,33 @@
         </is>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.1675586797136173</v>
+        <v>0.1576376103665817</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>0.2526776418799707</v>
+        <v>0.2465518609583436</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>0.5797636784064121</v>
+        <v>0.5958105286750749</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>0.7887338128707179</v>
+        <v>0.7574954747970096</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>1.679000614222018</v>
+        <v>1.708080623562378</v>
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
-          <t>0-1 (13.6%); 0-2 (11.9%); 1-1 (11.9%)</t>
+          <t>0-1 (14.0%); 0-2 (12.4%); 1-1 (11.5%)</t>
+        </is>
+      </c>
+      <c r="M23" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-18T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="N23" s="10" t="inlineStr">
+        <is>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -2020,23 +2252,33 @@
         </is>
       </c>
       <c r="G24" s="8" t="n">
-        <v>0.4939967606149677</v>
+        <v>0.4957793119350875</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>0.282765103935847</v>
+        <v>0.2798266210144562</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0.2232381354491853</v>
+        <v>0.2243940670504561</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>1.43514250455948</v>
+        <v>1.443119111401374</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.8779384845472145</v>
+        <v>0.8832115106380014</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
-          <t>1-0 (13.5%); 1-1 (13.2%); 0-0 (10.6%)</t>
+          <t>1-0 (13.5%); 1-1 (13.0%); 0-0 (10.4%)</t>
+        </is>
+      </c>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-17T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
     </row>
@@ -2072,23 +2314,33 @@
         </is>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.2292949684648357</v>
+        <v>0.2133268062699156</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>0.265358959901859</v>
+        <v>0.2619384371314675</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>0.5053460716333052</v>
+        <v>0.5247347565986168</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>0.985930710169286</v>
+        <v>0.9285593327596192</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>1.580696879668696</v>
+        <v>1.597688860675207</v>
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
-          <t>1-1 (12.6%); 0-1 (11.5%); 0-2 (9.6%)</t>
+          <t>1-1 (12.4%); 0-1 (12.2%); 0-2 (10.2%)</t>
+        </is>
+      </c>
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-17T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="N25" s="10" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
     </row>
@@ -2124,23 +2376,33 @@
         </is>
       </c>
       <c r="G26" s="8" t="n">
-        <v>0.4513619863953952</v>
+        <v>0.4604983526460637</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>0.2836049733594216</v>
+        <v>0.2837303868033567</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>0.2650330402451832</v>
+        <v>0.2557712605505796</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>1.399210414517756</v>
+        <v>1.391552823463772</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>1.011779003538674</v>
+        <v>0.9691310487563776</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
-          <t>1-1 (13.4%); 1-0 (11.8%); 0-0 (9.7%)</t>
+          <t>1-1 (13.3%); 1-0 (12.5%); 0-0 (10.0%)</t>
+        </is>
+      </c>
+      <c r="M26" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-18T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
     </row>
@@ -2176,23 +2438,33 @@
         </is>
       </c>
       <c r="G27" s="11" t="n">
-        <v>0.5487798653141968</v>
+        <v>0.5388761040234195</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>0.2560924152689516</v>
+        <v>0.2583281055128135</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>0.1951277194168518</v>
+        <v>0.202795790463767</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>1.664886909013396</v>
+        <v>1.629678813295301</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>0.895903136281673</v>
+        <v>0.904169970986084</v>
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>1-0 (12.2%); 1-1 (12.2%); 2-0 (10.7%)</t>
+          <t>1-0 (12.4%); 1-1 (12.3%); 2-0 (10.5%)</t>
+        </is>
+      </c>
+      <c r="M27" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-19T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="N27" s="10" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
     </row>
@@ -2228,23 +2500,33 @@
         </is>
       </c>
       <c r="G28" s="8" t="n">
-        <v>0.6736463135119627</v>
+        <v>0.6551886124497156</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>0.2104492667377964</v>
+        <v>0.2184210473306546</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>0.1159044197502409</v>
+        <v>0.1263903402196296</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>2.000064223980607</v>
+        <v>1.926609745224546</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.7025284335993174</v>
+        <v>0.718120244728978</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
-          <t>2-0 (13.4%); 1-0 (12.9%); 1-1 (9.9%)</t>
+          <t>1-0 (13.2%); 2-0 (13.2%); 1-1 (10.3%)</t>
+        </is>
+      </c>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-18T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
     </row>
@@ -2280,23 +2562,33 @@
         </is>
       </c>
       <c r="G29" s="11" t="n">
-        <v>0.7808724688162623</v>
+        <v>0.7608292985984598</v>
       </c>
       <c r="H29" s="11" t="n">
-        <v>0.1524442787420643</v>
+        <v>0.1615377094202169</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>0.0666832524416736</v>
+        <v>0.07763299198132299</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>2.479720896004731</v>
+        <v>2.410933606785732</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>0.6046289162901888</v>
+        <v>0.6492356952240528</v>
       </c>
       <c r="L29" s="10" t="inlineStr">
         <is>
-          <t>2-0 (14.1%); 3-0 (11.6%); 1-0 (11.0%)</t>
+          <t>2-0 (13.6%); 1-0 (10.9%); 3-0 (10.9%)</t>
+        </is>
+      </c>
+      <c r="M29" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-18T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="N29" s="10" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
     </row>
@@ -2332,23 +2624,33 @@
         </is>
       </c>
       <c r="G30" s="8" t="n">
-        <v>0.3824135998884024</v>
+        <v>0.3849466714456399</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>0.2955038069048092</v>
+        <v>0.2936714774627891</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>0.3220825932067883</v>
+        <v>0.3213818510915709</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>1.226546871557667</v>
+        <v>1.227915632383348</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>1.103657972114049</v>
+        <v>1.09851949579843</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
-          <t>1-1 (13.9%); 1-0 (11.2%); 0-0 (10.5%)</t>
+          <t>1-1 (13.8%); 1-0 (11.4%); 0-0 (10.4%)</t>
+        </is>
+      </c>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19T04:00:00Z</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="inlineStr">
+        <is>
+          <t>21:00</t>
         </is>
       </c>
     </row>
@@ -2384,23 +2686,33 @@
         </is>
       </c>
       <c r="G31" s="11" t="n">
-        <v>0.3602682920952369</v>
+        <v>0.3732965626113508</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>0.2778311508681899</v>
+        <v>0.2828857184064274</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>0.361900557036573</v>
+        <v>0.3438177189822217</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>1.298873618726413</v>
+        <v>1.275707023996948</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>1.302357871949876</v>
+        <v>1.213959291229454</v>
       </c>
       <c r="L31" s="10" t="inlineStr">
         <is>
-          <t>1-1 (13.2%); 0-1 (9.0%); 1-0 (8.9%)</t>
+          <t>1-1 (13.5%); 1-0 (10.0%); 0-1 (9.5%)</t>
+        </is>
+      </c>
+      <c r="M31" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-19T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="N31" s="10" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
     </row>
@@ -2436,23 +2748,33 @@
         </is>
       </c>
       <c r="G32" s="8" t="n">
-        <v>0.1829703940128424</v>
+        <v>0.1972797136016584</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>0.2740417029613821</v>
+        <v>0.2768818143677713</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0.5429879030257756</v>
+        <v>0.5258384720305704</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.7645325103494423</v>
+        <v>0.7973699882266951</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>1.508199237843173</v>
+        <v>1.47273378761834</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
-          <t>0-1 (14.9%); 1-1 (12.5%); 0-2 (11.7%)</t>
+          <t>0-1 (14.6%); 1-1 (12.7%); 0-2 (11.2%)</t>
+        </is>
+      </c>
+      <c r="M32" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="N32" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
     </row>
@@ -2488,23 +2810,33 @@
         </is>
       </c>
       <c r="G33" s="11" t="n">
-        <v>0.7207940888982639</v>
+        <v>0.7683029377741687</v>
       </c>
       <c r="H33" s="11" t="n">
-        <v>0.1777338042593958</v>
+        <v>0.1559724631089442</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>0.1014721068423401</v>
+        <v>0.075724599116887</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>2.349335336035468</v>
+        <v>2.48099031292108</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>0.7762327277069783</v>
+        <v>0.6637908309404704</v>
       </c>
       <c r="L33" s="10" t="inlineStr">
         <is>
-          <t>2-0 (12.1%); 1-0 (9.9%); 3-0 (9.5%)</t>
+          <t>2-0 (13.3%); 3-0 (11.0%); 1-0 (10.3%)</t>
+        </is>
+      </c>
+      <c r="M33" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-20T00:30:00Z</t>
+        </is>
+      </c>
+      <c r="N33" s="10" t="inlineStr">
+        <is>
+          <t>20:30</t>
         </is>
       </c>
     </row>
@@ -2540,23 +2872,33 @@
         </is>
       </c>
       <c r="G34" s="8" t="n">
-        <v>0.5038852487966238</v>
+        <v>0.5335071191667062</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>0.272047791561436</v>
+        <v>0.2625970722179966</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>0.2240669596419401</v>
+        <v>0.2038958086152971</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>1.522968210171694</v>
+        <v>1.591418419831002</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.9315230888103344</v>
+        <v>0.8873576857743276</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
-          <t>1-1 (12.9%); 1-0 (12.4%); 2-0 (10.0%)</t>
+          <t>1-0 (12.8%); 1-1 (12.4%); 2-0 (10.6%)</t>
+        </is>
+      </c>
+      <c r="M34" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-20T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="N34" s="7" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
     </row>
@@ -2592,23 +2934,33 @@
         </is>
       </c>
       <c r="G35" s="11" t="n">
-        <v>0.7119760782283782</v>
+        <v>0.7477917362702591</v>
       </c>
       <c r="H35" s="11" t="n">
-        <v>0.204329465516157</v>
+        <v>0.1804000604173547</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>0.0836944562554648</v>
+        <v>0.0718082033123862</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>1.946872878660312</v>
+        <v>2.12650419120663</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>0.5155965855654542</v>
+        <v>0.5087143912072086</v>
       </c>
       <c r="L35" s="10" t="inlineStr">
         <is>
-          <t>2-0 (16.2%); 1-0 (16.1%); 3-0 (10.5%)</t>
+          <t>2-0 (16.2%); 1-0 (14.9%); 3-0 (11.5%)</t>
+        </is>
+      </c>
+      <c r="M35" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-21T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="N35" s="10" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
     </row>
@@ -2644,23 +2996,33 @@
         </is>
       </c>
       <c r="G36" s="8" t="n">
-        <v>0.6353372815998667</v>
+        <v>0.6229397534919227</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>0.2122604414477653</v>
+        <v>0.2214266801192245</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0.1524022769523679</v>
+        <v>0.1556335663888526</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>2.080924585679361</v>
+        <v>1.959756117971529</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.9238491402029292</v>
+        <v>0.8737927774259624</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
-          <t>2-0 (10.7%); 1-1 (10.1%); 2-1 (9.9%)</t>
+          <t>2-0 (11.3%); 1-0 (11.0%); 1-1 (10.6%)</t>
+        </is>
+      </c>
+      <c r="M36" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-20T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="N36" s="7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
     </row>
@@ -2696,23 +3058,33 @@
         </is>
       </c>
       <c r="G37" s="11" t="n">
-        <v>0.142145896643749</v>
+        <v>0.1485341622803409</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>0.2433756367939537</v>
+        <v>0.2432634825430246</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>0.6144784665622972</v>
+        <v>0.6082023551766343</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>0.7058937668406049</v>
+        <v>0.7272618202839265</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>1.732723603165185</v>
+        <v>1.726683984767081</v>
       </c>
       <c r="L37" s="10" t="inlineStr">
         <is>
-          <t>0-1 (14.5%); 0-2 (13.1%); 1-1 (11.3%)</t>
+          <t>0-1 (14.3%); 0-2 (12.8%); 1-1 (11.3%)</t>
+        </is>
+      </c>
+      <c r="M37" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-20T04:00:00Z</t>
+        </is>
+      </c>
+      <c r="N37" s="10" t="inlineStr">
+        <is>
+          <t>22:00</t>
         </is>
       </c>
     </row>
@@ -2748,23 +3120,33 @@
         </is>
       </c>
       <c r="G38" s="8" t="n">
-        <v>0.4100455149318552</v>
+        <v>0.420367743007356</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>0.2804735619385333</v>
+        <v>0.2822604780161575</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0.3094809231296117</v>
+        <v>0.2973717789764865</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>1.370979824633999</v>
+        <v>1.357474447610061</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>1.158498952172883</v>
+        <v>1.10056059264015</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
-          <t>1-1 (13.4%); 1-0 (10.2%); 2-1 (8.7%)</t>
+          <t>1-1 (13.4%); 1-0 (11.0%); 0-0 (9.2%)</t>
+        </is>
+      </c>
+      <c r="M38" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-21T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="N38" s="7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
     </row>
@@ -2800,23 +3182,33 @@
         </is>
       </c>
       <c r="G39" s="11" t="n">
-        <v>0.2790359939620674</v>
+        <v>0.2841041717025396</v>
       </c>
       <c r="H39" s="11" t="n">
-        <v>0.2988927440411606</v>
+        <v>0.2969412423717591</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>0.422071261996772</v>
+        <v>0.4189545859257012</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>0.9767081135413226</v>
+        <v>0.9873359933956192</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>1.264157053429899</v>
+        <v>1.25847395280017</v>
       </c>
       <c r="L39" s="10" t="inlineStr">
         <is>
-          <t>1-1 (13.9%); 0-1 (12.7%); 0-0 (11.4%)</t>
+          <t>1-1 (13.8%); 0-1 (12.7%); 0-0 (11.2%)</t>
+        </is>
+      </c>
+      <c r="M39" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-22T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="N39" s="10" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
     </row>
@@ -2852,23 +3244,33 @@
         </is>
       </c>
       <c r="G40" s="8" t="n">
-        <v>0.7982468413723505</v>
+        <v>0.8242009717687088</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>0.1455583716124387</v>
+        <v>0.1297043960028507</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0.0561947870152107</v>
+        <v>0.0460946322284405</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>2.48527983917263</v>
+        <v>2.603841071751096</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.5309963951534724</v>
+        <v>0.4868290041678914</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
-          <t>2-0 (15.1%); 3-0 (12.5%); 1-0 (11.8%)</t>
+          <t>2-0 (15.4%); 3-0 (13.4%); 1-0 (11.6%)</t>
+        </is>
+      </c>
+      <c r="M40" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-21T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="N40" s="7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
     </row>
@@ -2904,23 +3306,33 @@
         </is>
       </c>
       <c r="G41" s="11" t="n">
-        <v>0.6250059269007412</v>
+        <v>0.6665215412207054</v>
       </c>
       <c r="H41" s="11" t="n">
-        <v>0.2472540969676812</v>
+        <v>0.2242558328816321</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>0.1277399761315774</v>
+        <v>0.1092226258976624</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>1.676954142789694</v>
+        <v>1.824743961129429</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>0.6187371293864694</v>
+        <v>0.5927558490251331</v>
       </c>
       <c r="L41" s="10" t="inlineStr">
         <is>
-          <t>1-0 (16.3%); 2-0 (14.2%); 1-1 (11.0%)</t>
+          <t>1-0 (15.8%); 2-0 (14.8%); 1-1 (10.1%)</t>
+        </is>
+      </c>
+      <c r="M41" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-21T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="N41" s="10" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
     </row>
@@ -2956,23 +3368,33 @@
         </is>
       </c>
       <c r="G42" s="8" t="n">
-        <v>0.2109190552406671</v>
+        <v>0.2264124441022119</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>0.2534579259586987</v>
+        <v>0.2610535454744687</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>0.5356230188006341</v>
+        <v>0.5125340104233194</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.977900701601062</v>
+        <v>0.9848385771724056</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>1.694447131692271</v>
+        <v>1.604409328189174</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
-          <t>1-1 (12.1%); 0-1 (11.1%); 0-2 (9.9%)</t>
+          <t>1-1 (12.4%); 0-1 (11.5%); 0-2 (9.7%)</t>
+        </is>
+      </c>
+      <c r="M42" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23T03:00:00Z</t>
+        </is>
+      </c>
+      <c r="N42" s="7" t="inlineStr">
+        <is>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -3008,23 +3430,33 @@
         </is>
       </c>
       <c r="G43" s="11" t="n">
-        <v>0.6294621173821918</v>
+        <v>0.661335036436596</v>
       </c>
       <c r="H43" s="11" t="n">
-        <v>0.2400145603003699</v>
+        <v>0.222169819709573</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>0.1305233223174383</v>
+        <v>0.1164951438538309</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>1.743778438577657</v>
+        <v>1.863274798803528</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>0.6597099268010769</v>
+        <v>0.6430818044870867</v>
       </c>
       <c r="L43" s="10" t="inlineStr">
         <is>
-          <t>1-0 (15.2%); 2-0 (13.7%); 1-1 (11.0%)</t>
+          <t>1-0 (14.7%); 2-0 (14.2%); 1-1 (10.2%)</t>
+        </is>
+      </c>
+      <c r="M43" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-22T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="N43" s="10" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
     </row>
@@ -3060,23 +3492,33 @@
         </is>
       </c>
       <c r="G44" s="8" t="n">
-        <v>0.3953119492739232</v>
+        <v>0.3937357769516895</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>0.2823823561732428</v>
+        <v>0.2871421930131156</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0.3223056945528339</v>
+        <v>0.3191220300351947</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>1.333987700699293</v>
+        <v>1.283985231427933</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>1.18028026157664</v>
+        <v>1.12963715860303</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
-          <t>1-1 (13.5%); 1-0 (10.1%); 0-1 (8.8%)</t>
+          <t>1-1 (13.6%); 1-0 (10.9%); 0-0 (9.6%)</t>
+        </is>
+      </c>
+      <c r="M44" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="N44" s="7" t="inlineStr">
+        <is>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -3112,23 +3554,33 @@
         </is>
       </c>
       <c r="G45" s="11" t="n">
-        <v>0.6756446426635373</v>
+        <v>0.7137538714129796</v>
       </c>
       <c r="H45" s="11" t="n">
-        <v>0.2160913590632789</v>
+        <v>0.1949992897950851</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>0.1082639982731837</v>
+        <v>0.0912468387919354</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>1.916935790598495</v>
+        <v>2.059885467560201</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>0.629114632155375</v>
+        <v>0.5943836102025195</v>
       </c>
       <c r="L45" s="10" t="inlineStr">
         <is>
-          <t>1-0 (14.5%); 2-0 (14.4%); 1-1 (10.0%)</t>
+          <t>2-0 (14.9%); 1-0 (14.1%); 3-0 (10.2%)</t>
+        </is>
+      </c>
+      <c r="M45" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-22T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="N45" s="10" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
     </row>
@@ -3164,23 +3616,33 @@
         </is>
       </c>
       <c r="G46" s="8" t="n">
-        <v>0.5683149531609867</v>
+        <v>0.5861038100978726</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>0.2596073442969982</v>
+        <v>0.25116177394465</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0.172077702542015</v>
+        <v>0.1627344159574773</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>1.62171825929526</v>
+        <v>1.672016240045337</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.7786728111043794</v>
+        <v>0.7614320338219339</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
-          <t>1-0 (14.1%); 1-1 (12.1%); 2-0 (11.9%)</t>
+          <t>1-0 (14.1%); 2-0 (12.3%); 1-1 (11.7%)</t>
+        </is>
+      </c>
+      <c r="M46" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="N46" s="7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
     </row>
@@ -3216,23 +3678,33 @@
         </is>
       </c>
       <c r="G47" s="11" t="n">
-        <v>0.5887378503856303</v>
+        <v>0.6375668722586878</v>
       </c>
       <c r="H47" s="11" t="n">
-        <v>0.2583637686830193</v>
+        <v>0.2352190575545631</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>0.1528983809313504</v>
+        <v>0.1272140701867489</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>1.616921496089453</v>
+        <v>1.76491059218062</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>0.6978059982978309</v>
+        <v>0.6505863961779876</v>
       </c>
       <c r="L47" s="10" t="inlineStr">
         <is>
-          <t>1-0 (15.4%); 2-0 (12.9%); 1-1 (11.8%)</t>
+          <t>1-0 (15.3%); 2-0 (13.9%); 1-1 (10.7%)</t>
+        </is>
+      </c>
+      <c r="M47" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-24T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="N47" s="10" t="inlineStr">
+        <is>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -3268,23 +3740,33 @@
         </is>
       </c>
       <c r="G48" s="8" t="n">
-        <v>0.7534960823348208</v>
+        <v>0.7851195867951355</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>0.1755565498658133</v>
+        <v>0.1552658685973821</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.070947367799366</v>
+        <v>0.0596145446074822</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>2.195940132716533</v>
+        <v>2.356195669435084</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.5311504449701444</v>
+        <v>0.5086899915990422</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
-          <t>2-0 (15.8%); 1-0 (13.9%); 3-0 (11.5%)</t>
+          <t>2-0 (15.8%); 1-0 (13.1%); 3-0 (12.4%)</t>
+        </is>
+      </c>
+      <c r="M48" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="N48" s="7" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
     </row>
@@ -3320,23 +3802,33 @@
         </is>
       </c>
       <c r="G49" s="11" t="n">
-        <v>0.2400383618344111</v>
+        <v>0.2309622669246815</v>
       </c>
       <c r="H49" s="11" t="n">
-        <v>0.2651132164380175</v>
+        <v>0.2658262688606158</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>0.4948484217275714</v>
+        <v>0.5032114642147026</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>1.027610101740962</v>
+        <v>0.976192617580525</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>1.579100762123792</v>
+        <v>1.559390379389032</v>
       </c>
       <c r="L49" s="10" t="inlineStr">
         <is>
-          <t>1-1 (12.6%); 0-1 (11.0%); 1-2 (9.5%)</t>
+          <t>1-1 (12.6%); 0-1 (11.8%); 0-2 (9.6%)</t>
+        </is>
+      </c>
+      <c r="M49" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-23T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="N49" s="10" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
     </row>
@@ -3372,23 +3864,33 @@
         </is>
       </c>
       <c r="G50" s="8" t="n">
-        <v>0.168068928540431</v>
+        <v>0.1582500332858072</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>0.2296332012891007</v>
+        <v>0.2316368433812804</v>
       </c>
       <c r="I50" s="8" t="n">
-        <v>0.6022978701704683</v>
+        <v>0.6101131233329121</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.908830030993196</v>
+        <v>0.8321509644660916</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>1.90825727993442</v>
+        <v>1.853564081134722</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
-          <t>1-1 (10.9%); 0-2 (10.9%); 0-1 (10.8%)</t>
+          <t>0-1 (12.1%); 0-2 (11.7%); 1-1 (11.0%)</t>
+        </is>
+      </c>
+      <c r="M50" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="N50" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
     </row>
@@ -3424,23 +3926,33 @@
         </is>
       </c>
       <c r="G51" s="11" t="n">
-        <v>0.6481736007895673</v>
+        <v>0.6653659384295703</v>
       </c>
       <c r="H51" s="11" t="n">
-        <v>0.2172669775862786</v>
+        <v>0.2105412475573069</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>0.134559421624154</v>
+        <v>0.1240928140131227</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>1.978231874758657</v>
+        <v>2.005785019205063</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>0.7852525097975708</v>
+        <v>0.7425903558983333</v>
       </c>
       <c r="L51" s="10" t="inlineStr">
         <is>
-          <t>2-0 (12.3%); 1-0 (11.9%); 1-1 (10.3%)</t>
+          <t>2-0 (12.9%); 1-0 (12.4%); 1-1 (10.0%)</t>
+        </is>
+      </c>
+      <c r="M51" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-25T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="N51" s="10" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
     </row>
@@ -3476,23 +3988,33 @@
         </is>
       </c>
       <c r="G52" s="8" t="n">
-        <v>0.1989960783942282</v>
+        <v>0.1722158741715398</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>0.2641540416394277</v>
+        <v>0.2506934601497001</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>0.536849879966344</v>
+        <v>0.57709066567876</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.8724165831940077</v>
+        <v>0.8073648282385372</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>1.593225075249436</v>
+        <v>1.68442364956102</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
-          <t>0-1 (12.9%); 1-1 (12.5%); 0-2 (10.8%)</t>
+          <t>0-1 (13.4%); 1-1 (11.8%); 0-2 (11.7%)</t>
+        </is>
+      </c>
+      <c r="M52" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="N52" s="7" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
     </row>
@@ -3528,23 +4050,33 @@
         </is>
       </c>
       <c r="G53" s="11" t="n">
-        <v>0.3998834746158988</v>
+        <v>0.4103157964500807</v>
       </c>
       <c r="H53" s="11" t="n">
-        <v>0.284913547134652</v>
+        <v>0.2805657902568708</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>0.3152029782494491</v>
+        <v>0.3091184132930483</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>1.323913412956819</v>
+        <v>1.35516445113346</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>1.146906532225555</v>
+        <v>1.142513401070024</v>
       </c>
       <c r="L53" s="10" t="inlineStr">
         <is>
-          <t>1-1 (13.5%); 1-0 (10.5%); 0-0 (9.2%)</t>
+          <t>1-1 (13.4%); 1-0 (10.5%); 0-0 (8.8%)</t>
+        </is>
+      </c>
+      <c r="M53" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-24T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="N53" s="10" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
     </row>
@@ -3580,23 +4112,33 @@
         </is>
       </c>
       <c r="G54" s="8" t="n">
-        <v>0.4295813560428497</v>
+        <v>0.4113299663141266</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>0.2848564302671793</v>
+        <v>0.285264530342248</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>0.285562213689971</v>
+        <v>0.3034055033436253</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>1.366283691903453</v>
+        <v>1.32383065634176</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>1.066473973582856</v>
+        <v>1.099912226638644</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
-          <t>1-1 (13.5%); 1-0 (11.3%); 0-0 (9.5%)</t>
+          <t>1-1 (13.5%); 1-0 (11.1%); 0-0 (9.5%)</t>
+        </is>
+      </c>
+      <c r="M54" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-24T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="N54" s="7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
     </row>
@@ -3632,23 +4174,33 @@
         </is>
       </c>
       <c r="G55" s="11" t="n">
-        <v>0.6580883665934811</v>
+        <v>0.6869361624199889</v>
       </c>
       <c r="H55" s="11" t="n">
-        <v>0.2237063342868881</v>
+        <v>0.2073371944451556</v>
       </c>
       <c r="I55" s="11" t="n">
-        <v>0.1182052991196309</v>
+        <v>0.1057266431348554</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>1.86935441687892</v>
+        <v>1.98198542759807</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>0.6574005855051784</v>
+        <v>0.6395106136109473</v>
       </c>
       <c r="L55" s="10" t="inlineStr">
         <is>
-          <t>1-0 (14.4%); 2-0 (14.0%); 1-1 (10.4%)</t>
+          <t>2-0 (14.3%); 1-0 (14.0%); 1-1 (9.7%)</t>
+        </is>
+      </c>
+      <c r="M55" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="N55" s="10" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
     </row>
@@ -3684,23 +4236,33 @@
         </is>
       </c>
       <c r="G56" s="8" t="n">
-        <v>0.1581906070695863</v>
+        <v>0.1535551007856017</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>0.2387929486997739</v>
+        <v>0.2378049589757785</v>
       </c>
       <c r="I56" s="8" t="n">
-        <v>0.6030164442306398</v>
+        <v>0.6086399402386194</v>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.8082207620907365</v>
+        <v>0.7770627872920459</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>1.798928558862065</v>
+        <v>1.784783874377552</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>0-1 (12.7%); 0-2 (11.9%); 1-1 (11.3%)</t>
+          <t>0-1 (13.3%); 0-2 (12.3%); 1-1 (11.2%)</t>
+        </is>
+      </c>
+      <c r="M56" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="N56" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
     </row>
@@ -3736,23 +4298,33 @@
         </is>
       </c>
       <c r="G57" s="11" t="n">
-        <v>0.6484845081093853</v>
+        <v>0.6234118435433191</v>
       </c>
       <c r="H57" s="11" t="n">
-        <v>0.2151155842769629</v>
+        <v>0.2261065440001063</v>
       </c>
       <c r="I57" s="11" t="n">
-        <v>0.1363999076136517</v>
+        <v>0.1504816124565746</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>2.007119383796166</v>
+        <v>1.898511699793602</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>0.8080009887487264</v>
+        <v>0.8188929819931108</v>
       </c>
       <c r="L57" s="10" t="inlineStr">
         <is>
-          <t>2-0 (12.1%); 1-0 (11.5%); 1-1 (10.3%)</t>
+          <t>1-0 (12.0%); 2-0 (11.9%); 1-1 (10.8%)</t>
+        </is>
+      </c>
+      <c r="M57" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-25T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="N57" s="10" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
     </row>
@@ -3788,23 +4360,33 @@
         </is>
       </c>
       <c r="G58" s="8" t="n">
-        <v>0.3602015674217815</v>
+        <v>0.3642991949209418</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>0.3104370423600334</v>
+        <v>0.3016004585792429</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>0.329361390218185</v>
+        <v>0.3341003464998154</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>1.103734984250782</v>
+        <v>1.145353640210175</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>1.043087701533573</v>
+        <v>1.085006307530701</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
-          <t>1-1 (14.2%); 0-0 (12.4%); 1-0 (12.1%)</t>
+          <t>1-1 (14.0%); 1-0 (11.7%); 0-0 (11.4%)</t>
+        </is>
+      </c>
+      <c r="M58" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="N58" s="7" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
     </row>
@@ -3840,23 +4422,33 @@
         </is>
       </c>
       <c r="G59" s="11" t="n">
-        <v>0.3624201858414443</v>
+        <v>0.4479373950115062</v>
       </c>
       <c r="H59" s="11" t="n">
-        <v>0.2630623959724067</v>
+        <v>0.2643737298025099</v>
       </c>
       <c r="I59" s="11" t="n">
-        <v>0.3745174181861488</v>
+        <v>0.2876888751859838</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>1.413839235905729</v>
+        <v>1.532263946323193</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>1.440742017575801</v>
+        <v>1.181979056817137</v>
       </c>
       <c r="L59" s="10" t="inlineStr">
         <is>
-          <t>1-1 (12.4%); 1-2 (8.4%); 2-1 (8.3%)</t>
+          <t>1-1 (12.6%); 1-0 (9.6%); 2-1 (9.2%)</t>
+        </is>
+      </c>
+      <c r="M59" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-26T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="N59" s="10" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
     </row>
@@ -3892,23 +4484,33 @@
         </is>
       </c>
       <c r="G60" s="8" t="n">
-        <v>0.326949951996777</v>
+        <v>0.2705415957729428</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>0.311781142688471</v>
+        <v>0.3008545166492923</v>
       </c>
       <c r="I60" s="8" t="n">
-        <v>0.361268905314752</v>
+        <v>0.4286038875777648</v>
       </c>
       <c r="J60" s="9" t="n">
-        <v>1.03150949971821</v>
+        <v>0.9323501712415736</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>1.098782670753855</v>
+        <v>1.246516320745882</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>1-1 (14.2%); 0-0 (12.6%); 0-1 (12.3%)</t>
+          <t>1-1 (13.8%); 0-1 (13.5%); 0-0 (11.9%)</t>
+        </is>
+      </c>
+      <c r="M60" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-26T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="N60" s="7" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
     </row>
@@ -3944,23 +4546,33 @@
         </is>
       </c>
       <c r="G61" s="11" t="n">
-        <v>0.1627676497530575</v>
+        <v>0.1614905383042707</v>
       </c>
       <c r="H61" s="11" t="n">
-        <v>0.2502147764837141</v>
+        <v>0.2479394999496945</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>0.5870175737632285</v>
+        <v>0.5905699617460347</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>0.7773508976434803</v>
+        <v>0.7697655369460646</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>1.696693785633641</v>
+        <v>1.699642882679103</v>
       </c>
       <c r="L61" s="10" t="inlineStr">
         <is>
-          <t>0-1 (13.7%); 0-2 (12.1%); 1-1 (11.7%)</t>
+          <t>0-1 (13.9%); 0-2 (12.2%); 1-1 (11.6%)</t>
+        </is>
+      </c>
+      <c r="M61" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-25T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="N61" s="10" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
     </row>
@@ -3996,23 +4608,33 @@
         </is>
       </c>
       <c r="G62" s="8" t="n">
-        <v>0.1788511793641036</v>
+        <v>0.1786589532225356</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>0.2650900570085204</v>
+        <v>0.260096489217624</v>
       </c>
       <c r="I62" s="8" t="n">
-        <v>0.5560587636273757</v>
+        <v>0.5612445575598405</v>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.7844440280711236</v>
+        <v>0.7936162234523837</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>1.579097054224177</v>
+        <v>1.605604864003466</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
-          <t>0-1 (14.2%); 1-1 (12.3%); 0-2 (11.7%)</t>
+          <t>0-1 (14.0%); 1-1 (12.1%); 0-2 (11.7%)</t>
+        </is>
+      </c>
+      <c r="M62" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-27T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="N62" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
     </row>
@@ -4048,23 +4670,33 @@
         </is>
       </c>
       <c r="G63" s="11" t="n">
-        <v>0.3054939191867138</v>
+        <v>0.3058389027711253</v>
       </c>
       <c r="H63" s="11" t="n">
-        <v>0.3042435162413539</v>
+        <v>0.3048557268939091</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>0.3902625645719323</v>
+        <v>0.3893053703349655</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>1.019107036922838</v>
+        <v>1.004674389835561</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>1.187949413000002</v>
+        <v>1.169880570335506</v>
       </c>
       <c r="L63" s="10" t="inlineStr">
         <is>
-          <t>1-1 (14.1%); 0-1 (12.3%); 0-0 (11.7%)</t>
+          <t>1-1 (14.0%); 0-1 (12.7%); 0-0 (12.0%)</t>
+        </is>
+      </c>
+      <c r="M63" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-27T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="N63" s="10" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
     </row>
@@ -4100,23 +4732,33 @@
         </is>
       </c>
       <c r="G64" s="8" t="n">
-        <v>0.275506074776578</v>
+        <v>0.2407472903508257</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>0.2699691437171386</v>
+        <v>0.2653110930375041</v>
       </c>
       <c r="I64" s="8" t="n">
-        <v>0.4545247815062832</v>
+        <v>0.4939416166116703</v>
       </c>
       <c r="J64" s="9" t="n">
-        <v>1.122038450095755</v>
+        <v>1.015221848042154</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>1.508478781337683</v>
+        <v>1.560221520476736</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>1-1 (12.9%); 0-1 (10.2%); 1-2 (9.2%)</t>
+          <t>1-1 (12.6%); 0-1 (11.3%); 1-2 (9.4%)</t>
+        </is>
+      </c>
+      <c r="M64" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-26T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="N64" s="7" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
     </row>
@@ -4152,23 +4794,33 @@
         </is>
       </c>
       <c r="G65" s="11" t="n">
-        <v>0.2755736384102117</v>
+        <v>0.2743848809344456</v>
       </c>
       <c r="H65" s="11" t="n">
-        <v>0.3015525652667263</v>
+        <v>0.2961491291581313</v>
       </c>
       <c r="I65" s="11" t="n">
-        <v>0.4228737963230619</v>
+        <v>0.4294659899074229</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>0.9549076978763126</v>
+        <v>0.9644820449677004</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>1.248913195512311</v>
+        <v>1.276347616992348</v>
       </c>
       <c r="L65" s="10" t="inlineStr">
         <is>
-          <t>1-1 (13.9%); 0-1 (13.1%); 0-0 (11.8%)</t>
+          <t>1-1 (13.7%); 0-1 (12.9%); 0-0 (11.3%)</t>
+        </is>
+      </c>
+      <c r="M65" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-27T03:00:00Z</t>
+        </is>
+      </c>
+      <c r="N65" s="10" t="inlineStr">
+        <is>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -4204,23 +4856,33 @@
         </is>
       </c>
       <c r="G66" s="8" t="n">
-        <v>0.1782587294252481</v>
+        <v>0.1718720974900319</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>0.2375214512744147</v>
+        <v>0.2394587711781463</v>
       </c>
       <c r="I66" s="8" t="n">
-        <v>0.584219819300337</v>
+        <v>0.5886691313318215</v>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.9167100854755802</v>
+        <v>0.8611237396656061</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>1.836430615743405</v>
+        <v>1.791584736506739</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
-          <t>1-1 (11.3%); 0-1 (11.1%); 0-2 (10.7%)</t>
+          <t>0-1 (12.1%); 1-1 (11.4%); 0-2 (11.3%)</t>
+        </is>
+      </c>
+      <c r="M66" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-27T03:00:00Z</t>
+        </is>
+      </c>
+      <c r="N66" s="7" t="inlineStr">
+        <is>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -4256,23 +4918,33 @@
         </is>
       </c>
       <c r="G67" s="11" t="n">
-        <v>0.5485377490468041</v>
+        <v>0.5460808008958372</v>
       </c>
       <c r="H67" s="11" t="n">
-        <v>0.2717289998051445</v>
+        <v>0.2711618814536015</v>
       </c>
       <c r="I67" s="11" t="n">
-        <v>0.1797332511480514</v>
+        <v>0.1827573176505612</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>1.525554813714764</v>
+        <v>1.516198069095261</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>0.7607609008528106</v>
+        <v>0.7642334776304056</v>
       </c>
       <c r="L67" s="10" t="inlineStr">
         <is>
-          <t>1-0 (14.8%); 1-1 (12.5%); 2-0 (11.8%)</t>
+          <t>1-0 (14.9%); 1-1 (12.4%); 2-0 (11.8%)</t>
+        </is>
+      </c>
+      <c r="M67" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-26T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="N67" s="10" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
     </row>
@@ -4308,23 +4980,33 @@
         </is>
       </c>
       <c r="G68" s="8" t="n">
-        <v>0.3217644622197912</v>
+        <v>0.3039757981322588</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>0.3333833689816816</v>
+        <v>0.3194560691543304</v>
       </c>
       <c r="I68" s="8" t="n">
-        <v>0.3448521687985271</v>
+        <v>0.3765681327134108</v>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.927410589931891</v>
+        <v>0.9356526374744594</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.9705622656006108</v>
+        <v>1.074671717330135</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
-          <t>0-0 (15.7%); 1-1 (14.2%); 0-1 (13.8%)</t>
+          <t>1-1 (14.1%); 0-0 (14.0%); 0-1 (13.7%)</t>
+        </is>
+      </c>
+      <c r="M68" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-27T23:30:00Z</t>
+        </is>
+      </c>
+      <c r="N68" s="7" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
     </row>
@@ -4360,23 +5042,33 @@
         </is>
       </c>
       <c r="G69" s="11" t="n">
-        <v>0.3789324339285978</v>
+        <v>0.3794207188200574</v>
       </c>
       <c r="H69" s="11" t="n">
-        <v>0.2791984987973977</v>
+        <v>0.284213306007033</v>
       </c>
       <c r="I69" s="11" t="n">
-        <v>0.3418690672740044</v>
+        <v>0.3363659751729096</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>1.327081598074603</v>
+        <v>1.278404481603934</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>1.248288984595728</v>
+        <v>1.188559899571743</v>
       </c>
       <c r="L69" s="10" t="inlineStr">
         <is>
-          <t>1-1 (13.3%); 1-0 (9.4%); 0-1 (8.8%)</t>
+          <t>1-1 (13.5%); 1-0 (10.2%); 0-1 (9.5%)</t>
+        </is>
+      </c>
+      <c r="M69" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-27T23:30:00Z</t>
+        </is>
+      </c>
+      <c r="N69" s="10" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
     </row>
@@ -4412,23 +5104,33 @@
         </is>
       </c>
       <c r="G70" s="8" t="n">
-        <v>0.1385795405347921</v>
+        <v>0.1333037257016839</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>0.2272452614628592</v>
+        <v>0.2222818934823762</v>
       </c>
       <c r="I70" s="8" t="n">
-        <v>0.6341751980023486</v>
+        <v>0.6444143808159397</v>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.7587802391382826</v>
+        <v>0.7404785696032532</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>1.881196957180355</v>
+        <v>1.903092385329933</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
-          <t>0-1 (12.9%); 0-2 (12.6%); 1-1 (10.8%)</t>
+          <t>0-1 (13.1%); 0-2 (12.9%); 1-1 (10.5%)</t>
+        </is>
+      </c>
+      <c r="M70" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-27T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="N70" s="7" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
     </row>
@@ -4464,23 +5166,33 @@
         </is>
       </c>
       <c r="G71" s="11" t="n">
-        <v>0.3910772530253146</v>
+        <v>0.3774946928026351</v>
       </c>
       <c r="H71" s="11" t="n">
-        <v>0.2957368446451308</v>
+        <v>0.2911899291242666</v>
       </c>
       <c r="I71" s="11" t="n">
-        <v>0.3131859023295545</v>
+        <v>0.3313153780730982</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>1.2394931192058</v>
+        <v>1.230190917024153</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>1.081044416784464</v>
+        <v>1.135543638259548</v>
       </c>
       <c r="L71" s="10" t="inlineStr">
         <is>
-          <t>1-1 (13.9%); 1-0 (11.4%); 0-0 (10.6%)</t>
+          <t>1-1 (13.7%); 1-0 (10.9%); 0-1 (10.0%)</t>
+        </is>
+      </c>
+      <c r="M71" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-28T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="N71" s="10" t="inlineStr">
+        <is>
+          <t>21:00</t>
         </is>
       </c>
     </row>
@@ -4516,23 +5228,33 @@
         </is>
       </c>
       <c r="G72" s="8" t="n">
-        <v>0.0696327362830544</v>
+        <v>0.0620492257374761</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>0.1565338398753846</v>
+        <v>0.1477386879201148</v>
       </c>
       <c r="I72" s="8" t="n">
-        <v>0.7738334238415608</v>
+        <v>0.7902120863424089</v>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.6116014121743628</v>
+        <v>0.5711918384655517</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>2.443089893211764</v>
+        <v>2.48870901194907</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
-          <t>0-2 (14.1%); 0-3 (11.5%); 0-1 (11.1%)</t>
+          <t>0-2 (14.5%); 0-3 (12.0%); 0-1 (11.3%)</t>
+        </is>
+      </c>
+      <c r="M72" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-28T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="N72" s="7" t="inlineStr">
+        <is>
+          <t>21:00</t>
         </is>
       </c>
     </row>
@@ -4568,23 +5290,33 @@
         </is>
       </c>
       <c r="G73" s="11" t="n">
-        <v>0.638227867309072</v>
+        <v>0.6705069560295404</v>
       </c>
       <c r="H73" s="11" t="n">
-        <v>0.2281678180152849</v>
+        <v>0.2135393803216437</v>
       </c>
       <c r="I73" s="11" t="n">
-        <v>0.1336043146756431</v>
+        <v>0.1159536636488161</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>1.861385271813381</v>
+        <v>1.94905187167149</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>0.7263904139883643</v>
+        <v>0.6770071932435888</v>
       </c>
       <c r="L73" s="10" t="inlineStr">
         <is>
-          <t>1-0 (13.4%); 2-0 (13.0%); 1-1 (10.7%)</t>
+          <t>2-0 (13.7%); 1-0 (13.6%); 1-1 (10.0%)</t>
+        </is>
+      </c>
+      <c r="M73" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-27T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="N73" s="10" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
     </row>
@@ -4705,217 +5437,217 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C2" s="7" t="n">
-        <v>2190</v>
+        <v>2219</v>
       </c>
       <c r="D2" s="9" t="n">
-        <v>0.8676725062334317</v>
+        <v>1.074392541708417</v>
       </c>
       <c r="E2" s="9" t="n">
-        <v>1.151700858698602</v>
+        <v>0.9409173585022012</v>
       </c>
       <c r="F2" s="9" t="n">
-        <v>6.649965</v>
+        <v>7.246165</v>
       </c>
       <c r="G2" s="8" t="n">
-        <v>0.68873</v>
+        <v>0.75499</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>0.21043</v>
+        <v>0.20556</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>0.078305</v>
+        <v>0.033635</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>0.022535</v>
+        <v>0.005815</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>0.96623</v>
+        <v>0.990035</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>0.681525</v>
+        <v>0.7097250000000001</v>
       </c>
       <c r="M2" s="8" t="n">
-        <v>0.52045</v>
+        <v>0.510755</v>
       </c>
       <c r="N2" s="8" t="n">
-        <v>0.380875</v>
+        <v>0.391375</v>
       </c>
       <c r="O2" s="8" t="n">
-        <v>0.25886</v>
+        <v>0.27262</v>
       </c>
       <c r="P2" s="8" t="n">
-        <v>0.171155</v>
+        <v>0.17706</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>2219</v>
+        <v>2190</v>
       </c>
       <c r="D3" s="12" t="n">
-        <v>0.9786417400620144</v>
+        <v>0.9820351293416092</v>
       </c>
       <c r="E3" s="12" t="n">
-        <v>0.788299789443239</v>
+        <v>1.27928908600315</v>
       </c>
       <c r="F3" s="12" t="n">
-        <v>7.129455</v>
+        <v>6.89114</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>0.75073</v>
+        <v>0.734545</v>
       </c>
       <c r="H3" s="11" t="n">
-        <v>0.200035</v>
+        <v>0.18664</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>0.040875</v>
+        <v>0.061565</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>0.008359999999999999</v>
+        <v>0.01725</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>0.98625</v>
+        <v>0.974945</v>
       </c>
       <c r="L3" s="11" t="n">
-        <v>0.676345</v>
+        <v>0.682575</v>
       </c>
       <c r="M3" s="11" t="n">
-        <v>0.48238</v>
+        <v>0.527595</v>
       </c>
       <c r="N3" s="11" t="n">
-        <v>0.361125</v>
+        <v>0.39007</v>
       </c>
       <c r="O3" s="11" t="n">
-        <v>0.24448</v>
+        <v>0.266515</v>
       </c>
       <c r="P3" s="11" t="n">
-        <v>0.15701</v>
+        <v>0.1749</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C4" s="7" t="n">
-        <v>2091</v>
+        <v>2125</v>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.6927352735646372</v>
+        <v>0.8876764133237766</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>0.95391744452111</v>
+        <v>0.8413997073510378</v>
       </c>
       <c r="F4" s="9" t="n">
-        <v>6.33173</v>
+        <v>5.92685</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>0.5989449999999999</v>
+        <v>0.536545</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>0.26728</v>
+        <v>0.2725</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.10409</v>
+        <v>0.142185</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>0.029685</v>
+        <v>0.04877</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>0.9537</v>
+        <v>0.926215</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>0.613555</v>
+        <v>0.6460050000000001</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>0.356905</v>
+        <v>0.40728</v>
       </c>
       <c r="N4" s="8" t="n">
-        <v>0.21091</v>
+        <v>0.25436</v>
       </c>
       <c r="O4" s="8" t="n">
-        <v>0.11859</v>
+        <v>0.139885</v>
       </c>
       <c r="P4" s="8" t="n">
-        <v>0.063555</v>
+        <v>0.07605000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>England</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>2125</v>
+        <v>2091</v>
       </c>
       <c r="D5" s="12" t="n">
-        <v>0.7842750356662183</v>
+        <v>0.8179724298921166</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>0.6906840151394514</v>
+        <v>1.055203369703185</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>5.61503</v>
+        <v>6.431035</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>0.475935</v>
+        <v>0.608995</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>0.286125</v>
+        <v>0.267785</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.17159</v>
+        <v>0.099435</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>0.06635000000000001</v>
+        <v>0.023785</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>0.8995300000000001</v>
+        <v>0.9614</v>
       </c>
       <c r="L5" s="11" t="n">
-        <v>0.6031</v>
+        <v>0.631235</v>
       </c>
       <c r="M5" s="11" t="n">
-        <v>0.367</v>
+        <v>0.369975</v>
       </c>
       <c r="N5" s="11" t="n">
-        <v>0.21876</v>
+        <v>0.22056</v>
       </c>
       <c r="O5" s="11" t="n">
-        <v>0.118995</v>
+        <v>0.12366</v>
       </c>
       <c r="P5" s="11" t="n">
-        <v>0.06339</v>
+        <v>0.06647</v>
       </c>
     </row>
     <row r="6">
@@ -4930,46 +5662,46 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>2069</v>
+        <v>2062</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.9179860856420669</v>
+        <v>1.021988056098562</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.6753088214576795</v>
+        <v>0.8927987583207913</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>5.787515</v>
+        <v>6.041775</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>0.48447</v>
+        <v>0.527195</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>0.31641</v>
+        <v>0.305855</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.146605</v>
+        <v>0.13074</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>0.052515</v>
+        <v>0.03621</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>0.920095</v>
+        <v>0.942345</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5976050000000001</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>0.35072</v>
+        <v>0.38057</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>0.20571</v>
+        <v>0.227515</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>0.108475</v>
+        <v>0.1194</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>0.05633</v>
+        <v>0.06223</v>
       </c>
     </row>
     <row r="7">
@@ -4987,205 +5719,205 @@
         <v>2064</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>0.8459412823794505</v>
+        <v>0.9252261113179164</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>0.6940126701335503</v>
+        <v>0.870216487331421</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>5.423645</v>
+        <v>5.599005</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>0.43724</v>
+        <v>0.45401</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>0.315905</v>
+        <v>0.32813</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.165965</v>
+        <v>0.15252</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>0.08089</v>
+        <v>0.06534</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>0.881905</v>
+        <v>0.9020049999999999</v>
       </c>
       <c r="L7" s="11" t="n">
-        <v>0.5753549999999999</v>
+        <v>0.59524</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.32145</v>
+        <v>0.3435</v>
       </c>
       <c r="N7" s="11" t="n">
-        <v>0.17562</v>
+        <v>0.186825</v>
       </c>
       <c r="O7" s="11" t="n">
-        <v>0.095405</v>
+        <v>0.10304</v>
       </c>
       <c r="P7" s="11" t="n">
-        <v>0.047965</v>
+        <v>0.05174</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>1985</v>
+        <v>2046</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.6042661089378955</v>
+        <v>0.9270949293823098</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>1.164454555585463</v>
+        <v>0.8208147648014446</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>5.38438</v>
+        <v>5.41159</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>0.37769</v>
+        <v>0.409065</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>0.36593</v>
+        <v>0.34553</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.186495</v>
+        <v>0.169395</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>0.069885</v>
+        <v>0.07600999999999999</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>0.88822</v>
+        <v>0.88626</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>0.51326</v>
+        <v>0.569395</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>0.307675</v>
+        <v>0.31387</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>0.172935</v>
+        <v>0.166075</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>0.086715</v>
+        <v>0.088065</v>
       </c>
       <c r="P8" s="8" t="n">
-        <v>0.042455</v>
+        <v>0.04257</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>0.7734108894513042</v>
+        <v>0.6422554069424886</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>0.9070108853568424</v>
+        <v>1.181200587972159</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>5.679635</v>
+        <v>5.304125</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>0.456665</v>
+        <v>0.345695</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0.330495</v>
+        <v>0.38535</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.151665</v>
+        <v>0.201395</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>0.061175</v>
+        <v>0.06756</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>0.907695</v>
+        <v>0.88761</v>
       </c>
       <c r="L9" s="11" t="n">
-        <v>0.489985</v>
+        <v>0.497855</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.300045</v>
+        <v>0.292515</v>
       </c>
       <c r="N9" s="11" t="n">
-        <v>0.16625</v>
+        <v>0.15686</v>
       </c>
       <c r="O9" s="11" t="n">
-        <v>0.082875</v>
+        <v>0.07333000000000001</v>
       </c>
       <c r="P9" s="11" t="n">
-        <v>0.040975</v>
+        <v>0.033405</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>2046</v>
+        <v>1994</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.8198143554106646</v>
+        <v>0.865079566767667</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.6874635567096956</v>
+        <v>0.9111837558442168</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>5.257015</v>
+        <v>5.53836</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>0.399095</v>
+        <v>0.432265</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>0.32951</v>
+        <v>0.33571</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0.18044</v>
+        <v>0.162575</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>0.09095499999999999</v>
+        <v>0.06945</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>0.866645</v>
+        <v>0.89695</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>0.54993</v>
+        <v>0.46548</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>0.296365</v>
+        <v>0.27877</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>0.15856</v>
+        <v>0.14674</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>0.08395</v>
+        <v>0.068305</v>
       </c>
       <c r="P10" s="8" t="n">
-        <v>0.04089</v>
+        <v>0.031385</v>
       </c>
     </row>
     <row r="11">
@@ -5203,43 +5935,43 @@
         <v>2028</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>0.3416380883018513</v>
+        <v>0.4594995334200104</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>1.083022812962857</v>
+        <v>1.098483017806198</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>5.45213</v>
+        <v>5.6244</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>0.394425</v>
+        <v>0.41523</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>0.34455</v>
+        <v>0.351095</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.204865</v>
+        <v>0.188225</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>0.05616</v>
+        <v>0.04545</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>0.90101</v>
+        <v>0.91854</v>
       </c>
       <c r="L11" s="11" t="n">
-        <v>0.5163</v>
+        <v>0.533585</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.27222</v>
+        <v>0.279</v>
       </c>
       <c r="N11" s="11" t="n">
-        <v>0.144325</v>
+        <v>0.148395</v>
       </c>
       <c r="O11" s="11" t="n">
-        <v>0.06940499999999999</v>
+        <v>0.06815499999999999</v>
       </c>
       <c r="P11" s="11" t="n">
-        <v>0.032105</v>
+        <v>0.03057</v>
       </c>
     </row>
     <row r="12">
@@ -5257,43 +5989,43 @@
         <v>2005</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.8602872138261374</v>
+        <v>0.9434179850777538</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.5614510992684035</v>
+        <v>0.6446755183066669</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>5.52947</v>
+        <v>5.664715</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>0.427675</v>
+        <v>0.434815</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>0.325185</v>
+        <v>0.339145</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.19431</v>
+        <v>0.183095</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>0.05283</v>
+        <v>0.042945</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>0.912025</v>
+        <v>0.925235</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>0.51983</v>
+        <v>0.53148</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>0.269215</v>
+        <v>0.271335</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>0.140355</v>
+        <v>0.141565</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>0.064565</v>
+        <v>0.0635</v>
       </c>
       <c r="P12" s="8" t="n">
-        <v>0.029525</v>
+        <v>0.028095</v>
       </c>
     </row>
     <row r="13">
@@ -5311,43 +6043,43 @@
         <v>2011</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>0.8161529964685215</v>
+        <v>0.8994742059570936</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>0.6067885066121175</v>
+        <v>0.7006174541361242</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>5.453395</v>
+        <v>5.497355</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>0.40879</v>
+        <v>0.42504</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>0.34889</v>
+        <v>0.33763</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.168275</v>
+        <v>0.164395</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>0.074045</v>
+        <v>0.072935</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>0.888825</v>
+        <v>0.892285</v>
       </c>
       <c r="L13" s="11" t="n">
-        <v>0.45352</v>
+        <v>0.45448</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.26331</v>
+        <v>0.2689</v>
       </c>
       <c r="N13" s="11" t="n">
-        <v>0.13754</v>
+        <v>0.13945</v>
       </c>
       <c r="O13" s="11" t="n">
-        <v>0.06372</v>
+        <v>0.0624</v>
       </c>
       <c r="P13" s="11" t="n">
-        <v>0.029035</v>
+        <v>0.027585</v>
       </c>
     </row>
     <row r="14">
@@ -5362,370 +6094,370 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>1980</v>
+        <v>1988</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.5217326504938441</v>
+        <v>0.5960747025661201</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.765889914867255</v>
+        <v>0.8011939833766032</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>6.406305</v>
+        <v>6.493745</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>0.636405</v>
+        <v>0.64407</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>0.23722</v>
+        <v>0.239615</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0.093835</v>
+        <v>0.08903999999999999</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>0.03254</v>
+        <v>0.027275</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>0.952385</v>
+        <v>0.95903</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>0.631355</v>
+        <v>0.651085</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>0.347015</v>
+        <v>0.355245</v>
       </c>
       <c r="N14" s="8" t="n">
-        <v>0.15688</v>
+        <v>0.159515</v>
       </c>
       <c r="O14" s="8" t="n">
-        <v>0.06808</v>
+        <v>0.066765</v>
       </c>
       <c r="P14" s="8" t="n">
-        <v>0.028465</v>
+        <v>0.02693</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1972</v>
+        <v>1957</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>0.8065836366768705</v>
+        <v>0.8380106911714965</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>0.6004475726943</v>
+        <v>0.7267831145481238</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>4.579885</v>
+        <v>5.33011</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>0.27396</v>
+        <v>0.443335</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>0.314785</v>
+        <v>0.28247</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.26965</v>
+        <v>0.176365</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>0.141605</v>
+        <v>0.09783</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>0.78822</v>
+        <v>0.866885</v>
       </c>
       <c r="L15" s="11" t="n">
-        <v>0.4407</v>
+        <v>0.5206</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.221635</v>
+        <v>0.254185</v>
       </c>
       <c r="N15" s="11" t="n">
-        <v>0.108015</v>
+        <v>0.103385</v>
       </c>
       <c r="O15" s="11" t="n">
-        <v>0.04822</v>
+        <v>0.046795</v>
       </c>
       <c r="P15" s="11" t="n">
-        <v>0.02054</v>
+        <v>0.018835</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>1957</v>
+        <v>1976</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.7688397170785906</v>
+        <v>0.5361403190357032</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.6024234694351522</v>
+        <v>0.9993795843513668</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>5.233945</v>
+        <v>5.09071</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>0.42708</v>
+        <v>0.209145</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>0.282415</v>
+        <v>0.54923</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0.184435</v>
+        <v>0.18231</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>0.10607</v>
+        <v>0.059315</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>0.85544</v>
+        <v>0.88295</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>0.506815</v>
+        <v>0.37715</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>0.251935</v>
+        <v>0.20305</v>
       </c>
       <c r="N16" s="8" t="n">
-        <v>0.106545</v>
+        <v>0.10317</v>
       </c>
       <c r="O16" s="8" t="n">
-        <v>0.048665</v>
+        <v>0.046755</v>
       </c>
       <c r="P16" s="8" t="n">
-        <v>0.019995</v>
+        <v>0.018575</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>1956</v>
+        <v>1878</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>0.7036300424154058</v>
+        <v>0.6197080298249964</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>0.5803301084750881</v>
+        <v>0.5008217913290806</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>5.890855</v>
+        <v>4.674895</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>0.42121</v>
+        <v>0.34216</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>0.418985</v>
+        <v>0.27167</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.12519</v>
+        <v>0.21715</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>0.034615</v>
+        <v>0.16902</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>0.93916</v>
+        <v>0.781875</v>
       </c>
       <c r="L17" s="11" t="n">
-        <v>0.55357</v>
+        <v>0.475125</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.25873</v>
+        <v>0.229525</v>
       </c>
       <c r="N17" s="11" t="n">
-        <v>0.10947</v>
+        <v>0.09485499999999999</v>
       </c>
       <c r="O17" s="11" t="n">
-        <v>0.04704</v>
+        <v>0.04215</v>
       </c>
       <c r="P17" s="11" t="n">
-        <v>0.018755</v>
+        <v>0.01645</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>1976</v>
+        <v>1972</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.3427403658328566</v>
+        <v>0.8167179039022039</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.8722129040356873</v>
+        <v>0.6311780507129194</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>4.885175</v>
+        <v>4.464975</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>0.19987</v>
+        <v>0.243875</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>0.5152600000000001</v>
+        <v>0.32653</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>0.207985</v>
+        <v>0.28316</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>0.076885</v>
+        <v>0.146435</v>
       </c>
       <c r="K18" s="8" t="n">
-        <v>0.85407</v>
+        <v>0.77888</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>0.355055</v>
+        <v>0.417055</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>0.1846</v>
+        <v>0.202265</v>
       </c>
       <c r="N18" s="8" t="n">
-        <v>0.08982999999999999</v>
+        <v>0.09407</v>
       </c>
       <c r="O18" s="8" t="n">
-        <v>0.03959</v>
+        <v>0.038645</v>
       </c>
       <c r="P18" s="8" t="n">
-        <v>0.015675</v>
+        <v>0.01512</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>1899</v>
+        <v>1956</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>0.4316840166783687</v>
+        <v>0.6243845839645937</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>0.7003306571003473</v>
+        <v>0.7888178065690805</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>6.28332</v>
+        <v>4.456375</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.51856</v>
+        <v>0.29885</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>0.361005</v>
+        <v>0.27369</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>0.096895</v>
+        <v>0.23667</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>0.02354</v>
+        <v>0.19079</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>0.958425</v>
+        <v>0.752115</v>
       </c>
       <c r="L19" s="11" t="n">
-        <v>0.556775</v>
+        <v>0.43782</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>0.26301</v>
+        <v>0.204375</v>
       </c>
       <c r="N19" s="11" t="n">
-        <v>0.096595</v>
+        <v>0.083625</v>
       </c>
       <c r="O19" s="11" t="n">
-        <v>0.03603</v>
+        <v>0.03571</v>
       </c>
       <c r="P19" s="11" t="n">
-        <v>0.012975</v>
+        <v>0.013445</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>1914</v>
+        <v>1932</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.6889802558172295</v>
+        <v>0.7505639298074464</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.7060775568469556</v>
+        <v>0.639403375932344</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>4.14828</v>
+        <v>5.723065</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>0.20863</v>
+        <v>0.398755</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>0.290285</v>
+        <v>0.41576</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>0.31661</v>
+        <v>0.14053</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>0.184475</v>
+        <v>0.044955</v>
       </c>
       <c r="K20" s="8" t="n">
-        <v>0.7248</v>
+        <v>0.924775</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>0.374145</v>
+        <v>0.524365</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>0.176025</v>
+        <v>0.231985</v>
       </c>
       <c r="N20" s="8" t="n">
-        <v>0.07863000000000001</v>
+        <v>0.08928999999999999</v>
       </c>
       <c r="O20" s="8" t="n">
-        <v>0.03289</v>
+        <v>0.03546</v>
       </c>
       <c r="P20" s="8" t="n">
-        <v>0.012955</v>
+        <v>0.012815</v>
       </c>
     </row>
     <row r="21">
@@ -5743,319 +6475,319 @@
         <v>1969</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>0.5699861469467729</v>
+        <v>0.660794700492303</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>0.5551890796089411</v>
+        <v>0.6813807678904417</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>4.842275</v>
+        <v>4.95143</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>0.267095</v>
+        <v>0.27021</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>0.39104</v>
+        <v>0.40699</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>0.241115</v>
+        <v>0.236465</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>0.10075</v>
+        <v>0.086335</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>0.83594</v>
+        <v>0.854325</v>
       </c>
       <c r="L21" s="11" t="n">
-        <v>0.398335</v>
+        <v>0.41437</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>0.1664</v>
+        <v>0.175365</v>
       </c>
       <c r="N21" s="11" t="n">
-        <v>0.0743</v>
+        <v>0.079945</v>
       </c>
       <c r="O21" s="11" t="n">
-        <v>0.030685</v>
+        <v>0.033445</v>
       </c>
       <c r="P21" s="11" t="n">
-        <v>0.0116</v>
+        <v>0.012265</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>1885</v>
+        <v>1914</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.7076665631277939</v>
+        <v>0.6730218565392126</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.7357437243241307</v>
+        <v>0.8057024174985312</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>4.026315</v>
+        <v>4.035415</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>0.15529</v>
+        <v>0.18287</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>0.35139</v>
+        <v>0.29419</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>0.30644</v>
+        <v>0.332475</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>0.18688</v>
+        <v>0.190465</v>
       </c>
       <c r="K22" s="8" t="n">
-        <v>0.714995</v>
+        <v>0.7125899999999999</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>0.2971</v>
+        <v>0.350825</v>
       </c>
       <c r="M22" s="8" t="n">
-        <v>0.147615</v>
+        <v>0.15774</v>
       </c>
       <c r="N22" s="8" t="n">
-        <v>0.06691999999999999</v>
+        <v>0.06633500000000001</v>
       </c>
       <c r="O22" s="8" t="n">
-        <v>0.027915</v>
+        <v>0.02563</v>
       </c>
       <c r="P22" s="8" t="n">
-        <v>0.01035</v>
+        <v>0.009220000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>1897</v>
+        <v>1876</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>0.6575614054634855</v>
+        <v>0.5650963188659137</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>0.6171550786183537</v>
+        <v>0.7181851934626273</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>4.63744</v>
+        <v>6.248805</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.31062</v>
+        <v>0.52981</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>0.298365</v>
+        <v>0.341055</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>0.235155</v>
+        <v>0.101385</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>0.15586</v>
+        <v>0.02775</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>0.7852</v>
+        <v>0.953965</v>
       </c>
       <c r="L23" s="11" t="n">
-        <v>0.41524</v>
+        <v>0.545715</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>0.181875</v>
+        <v>0.24653</v>
       </c>
       <c r="N23" s="11" t="n">
-        <v>0.06872</v>
+        <v>0.081285</v>
       </c>
       <c r="O23" s="11" t="n">
-        <v>0.027785</v>
+        <v>0.027975</v>
       </c>
       <c r="P23" s="11" t="n">
-        <v>0.01004</v>
+        <v>0.00906</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>1902</v>
+        <v>1897</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.5503725432767741</v>
+        <v>0.70921884142574</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>0.7027483282990135</v>
+        <v>0.6932337769741979</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>4.115365</v>
+        <v>4.610695</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>0.253215</v>
+        <v>0.302935</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>0.254845</v>
+        <v>0.302045</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0.250745</v>
+        <v>0.237675</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>0.241195</v>
+        <v>0.157345</v>
       </c>
       <c r="K24" s="8" t="n">
-        <v>0.69434</v>
+        <v>0.784325</v>
       </c>
       <c r="L24" s="8" t="n">
-        <v>0.374875</v>
+        <v>0.408605</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>0.166045</v>
+        <v>0.169215</v>
       </c>
       <c r="N24" s="8" t="n">
-        <v>0.065355</v>
+        <v>0.059445</v>
       </c>
       <c r="O24" s="8" t="n">
-        <v>0.026295</v>
+        <v>0.022755</v>
       </c>
       <c r="P24" s="8" t="n">
-        <v>0.00991</v>
+        <v>0.00779</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1969</v>
+        <v>1904</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>0.6259427245157326</v>
+        <v>0.6397825872343607</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>0.4175873712510592</v>
+        <v>0.5731614998391557</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>4.19187</v>
+        <v>4.582255</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.270185</v>
+        <v>0.227195</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>0.252295</v>
+        <v>0.391555</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>0.243925</v>
+        <v>0.25155</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>0.233595</v>
+        <v>0.1297</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>0.705095</v>
+        <v>0.79945</v>
       </c>
       <c r="L25" s="11" t="n">
-        <v>0.387195</v>
+        <v>0.428975</v>
       </c>
       <c r="M25" s="11" t="n">
-        <v>0.17288</v>
+        <v>0.17435</v>
       </c>
       <c r="N25" s="11" t="n">
-        <v>0.06719</v>
+        <v>0.06292</v>
       </c>
       <c r="O25" s="11" t="n">
-        <v>0.026925</v>
+        <v>0.02162</v>
       </c>
       <c r="P25" s="11" t="n">
-        <v>0.009875</v>
+        <v>0.00738</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>1827</v>
+        <v>1885</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.5462458218798337</v>
+        <v>0.7415995293658445</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>0.3260398820305129</v>
+        <v>0.7148874498198743</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>4.12912</v>
+        <v>3.821605</v>
       </c>
       <c r="G26" s="8" t="n">
-        <v>0.263025</v>
+        <v>0.12454</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>0.250985</v>
+        <v>0.3469</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>0.242785</v>
+        <v>0.319185</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>0.243205</v>
+        <v>0.209375</v>
       </c>
       <c r="K26" s="8" t="n">
-        <v>0.69607</v>
+        <v>0.683285</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>0.37789</v>
+        <v>0.25189</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>0.16354</v>
+        <v>0.114775</v>
       </c>
       <c r="N26" s="8" t="n">
-        <v>0.06272999999999999</v>
+        <v>0.047565</v>
       </c>
       <c r="O26" s="8" t="n">
-        <v>0.024965</v>
+        <v>0.0181</v>
       </c>
       <c r="P26" s="8" t="n">
-        <v>0.008869999999999999</v>
+        <v>0.00581</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
@@ -6064,154 +6796,154 @@
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>1919</v>
+        <v>1916</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>0.3592362412259278</v>
+        <v>0.669485800157237</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>0.681821963223522</v>
+        <v>0.4347688342494668</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>3.84315</v>
+        <v>3.741415</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>0.213575</v>
+        <v>0.20004</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>0.241875</v>
+        <v>0.23649</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>0.262545</v>
+        <v>0.26932</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>0.282005</v>
+        <v>0.29415</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>0.64677</v>
+        <v>0.6322950000000001</v>
       </c>
       <c r="L27" s="11" t="n">
-        <v>0.329145</v>
+        <v>0.318495</v>
       </c>
       <c r="M27" s="11" t="n">
-        <v>0.13625</v>
+        <v>0.12369</v>
       </c>
       <c r="N27" s="11" t="n">
-        <v>0.05185</v>
+        <v>0.043065</v>
       </c>
       <c r="O27" s="11" t="n">
-        <v>0.02</v>
+        <v>0.015205</v>
       </c>
       <c r="P27" s="11" t="n">
-        <v>0.00699</v>
+        <v>0.00466</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C28" s="7" t="n">
-        <v>1881</v>
+        <v>1890</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.5683883591013845</v>
+        <v>0.5934594125208246</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.4800497973247077</v>
+        <v>0.6735342943987382</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>4.368295</v>
+        <v>3.6255</v>
       </c>
       <c r="G28" s="8" t="n">
-        <v>0.210075</v>
+        <v>0.106865</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>0.364675</v>
+        <v>0.31827</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>0.26692</v>
+        <v>0.33913</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>0.15833</v>
+        <v>0.235735</v>
       </c>
       <c r="K28" s="8" t="n">
-        <v>0.76208</v>
+        <v>0.64506</v>
       </c>
       <c r="L28" s="8" t="n">
-        <v>0.383395</v>
+        <v>0.226925</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>0.150745</v>
+        <v>0.09819</v>
       </c>
       <c r="N28" s="8" t="n">
-        <v>0.05337</v>
+        <v>0.037295</v>
       </c>
       <c r="O28" s="8" t="n">
-        <v>0.018455</v>
+        <v>0.01356</v>
       </c>
       <c r="P28" s="8" t="n">
-        <v>0.005895</v>
+        <v>0.004205</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1890</v>
+        <v>1867</v>
       </c>
       <c r="D29" s="12" t="n">
-        <v>0.5310022466443759</v>
+        <v>0.3810822084379557</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>0.646577779298098</v>
+        <v>0.7461862636816744</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>3.638135</v>
+        <v>3.424235</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>0.117505</v>
+        <v>0.15895</v>
       </c>
       <c r="H29" s="11" t="n">
-        <v>0.30042</v>
+        <v>0.21815</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>0.34327</v>
+        <v>0.27686</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>0.238805</v>
+        <v>0.34604</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>0.64462</v>
+        <v>0.573105</v>
       </c>
       <c r="L29" s="11" t="n">
-        <v>0.24719</v>
+        <v>0.268385</v>
       </c>
       <c r="M29" s="11" t="n">
-        <v>0.113265</v>
+        <v>0.09803000000000001</v>
       </c>
       <c r="N29" s="11" t="n">
-        <v>0.045765</v>
+        <v>0.033165</v>
       </c>
       <c r="O29" s="11" t="n">
-        <v>0.017495</v>
+        <v>0.01099</v>
       </c>
       <c r="P29" s="11" t="n">
-        <v>0.00588</v>
+        <v>0.003335</v>
       </c>
     </row>
     <row r="30">
@@ -6229,151 +6961,151 @@
         <v>1816</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.4230395510353553</v>
+        <v>0.4523824912789921</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0.7200675286621008</v>
+        <v>0.739444376491197</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>3.921595</v>
+        <v>3.79397</v>
       </c>
       <c r="G30" s="8" t="n">
-        <v>0.15767</v>
+        <v>0.134225</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>0.2669</v>
+        <v>0.254555</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>0.402835</v>
+        <v>0.434185</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>0.172595</v>
+        <v>0.177035</v>
       </c>
       <c r="K30" s="8" t="n">
-        <v>0.708345</v>
+        <v>0.692145</v>
       </c>
       <c r="L30" s="8" t="n">
-        <v>0.28352</v>
+        <v>0.258185</v>
       </c>
       <c r="M30" s="8" t="n">
-        <v>0.10483</v>
+        <v>0.08878</v>
       </c>
       <c r="N30" s="8" t="n">
-        <v>0.037295</v>
+        <v>0.02893</v>
       </c>
       <c r="O30" s="8" t="n">
-        <v>0.011985</v>
+        <v>0.00817</v>
       </c>
       <c r="P30" s="8" t="n">
-        <v>0.00393</v>
+        <v>0.00231</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>1811</v>
+        <v>1863</v>
       </c>
       <c r="D31" s="12" t="n">
-        <v>0.2956661536026934</v>
+        <v>0.4898950790125121</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>0.7257892991757379</v>
+        <v>0.4625698066337363</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>3.678295</v>
+        <v>3.364055</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>0.168255</v>
+        <v>0.1009</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>0.250465</v>
+        <v>0.222955</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>0.306365</v>
+        <v>0.413545</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>0.274915</v>
+        <v>0.2626</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>0.631515</v>
+        <v>0.59748</v>
       </c>
       <c r="L31" s="11" t="n">
-        <v>0.26751</v>
+        <v>0.210725</v>
       </c>
       <c r="M31" s="11" t="n">
-        <v>0.09358</v>
+        <v>0.080265</v>
       </c>
       <c r="N31" s="11" t="n">
-        <v>0.029205</v>
+        <v>0.026495</v>
       </c>
       <c r="O31" s="11" t="n">
-        <v>0.009509999999999999</v>
+        <v>0.007315</v>
       </c>
       <c r="P31" s="11" t="n">
-        <v>0.002865</v>
+        <v>0.00198</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C32" s="7" t="n">
-        <v>1844</v>
+        <v>1811</v>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.4919309455800118</v>
+        <v>0.3652033586461987</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>0.3976747402485445</v>
+        <v>0.766520337544809</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>3.22908</v>
+        <v>3.61768</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>0.09933500000000001</v>
+        <v>0.161315</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>0.209085</v>
+        <v>0.24582</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0.387675</v>
+        <v>0.307915</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>0.303905</v>
+        <v>0.28495</v>
       </c>
       <c r="K32" s="8" t="n">
-        <v>0.56069</v>
+        <v>0.62273</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>0.19742</v>
+        <v>0.25712</v>
       </c>
       <c r="M32" s="8" t="n">
-        <v>0.07550999999999999</v>
+        <v>0.08344500000000001</v>
       </c>
       <c r="N32" s="8" t="n">
-        <v>0.024835</v>
+        <v>0.024005</v>
       </c>
       <c r="O32" s="8" t="n">
-        <v>0.007415</v>
+        <v>0.007285</v>
       </c>
       <c r="P32" s="8" t="n">
-        <v>0.002115</v>
+        <v>0.0019</v>
       </c>
     </row>
     <row r="33">
@@ -6391,211 +7123,211 @@
         <v>1821</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>0.2592803286212962</v>
+        <v>0.3488609142935172</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>0.6167335605946724</v>
+        <v>0.6954071816755016</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>2.89785</v>
+        <v>2.908125</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>0.086475</v>
+        <v>0.08061500000000001</v>
       </c>
       <c r="H33" s="11" t="n">
-        <v>0.183175</v>
+        <v>0.18205</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>0.329085</v>
+        <v>0.356125</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>0.401265</v>
+        <v>0.38121</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0.472385</v>
+        <v>0.48315</v>
       </c>
       <c r="L33" s="11" t="n">
-        <v>0.1784</v>
+        <v>0.175105</v>
       </c>
       <c r="M33" s="11" t="n">
-        <v>0.05521</v>
+        <v>0.053475</v>
       </c>
       <c r="N33" s="11" t="n">
-        <v>0.01871</v>
+        <v>0.017125</v>
       </c>
       <c r="O33" s="11" t="n">
-        <v>0.0057</v>
+        <v>0.005185</v>
       </c>
       <c r="P33" s="11" t="n">
-        <v>0.001525</v>
+        <v>0.001315</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C34" s="7" t="n">
-        <v>1764</v>
+        <v>1854</v>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.1862399204230019</v>
+        <v>0.4588116933738216</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>0.7764958076546168</v>
+        <v>0.298282134496713</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>2.77356</v>
+        <v>3.422615</v>
       </c>
       <c r="G34" s="8" t="n">
-        <v>0.07718999999999999</v>
+        <v>0.09927999999999999</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>0.17141</v>
+        <v>0.238945</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>0.32451</v>
+        <v>0.4145</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>0.42689</v>
+        <v>0.247275</v>
       </c>
       <c r="K34" s="8" t="n">
-        <v>0.44694</v>
+        <v>0.6096</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>0.16311</v>
+        <v>0.188725</v>
       </c>
       <c r="M34" s="8" t="n">
-        <v>0.04879</v>
+        <v>0.056055</v>
       </c>
       <c r="N34" s="8" t="n">
-        <v>0.015575</v>
+        <v>0.0162</v>
       </c>
       <c r="O34" s="8" t="n">
-        <v>0.00447</v>
+        <v>0.00449</v>
       </c>
       <c r="P34" s="8" t="n">
-        <v>0.001245</v>
+        <v>0.00114</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>1854</v>
+        <v>1779</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>0.4298005279805361</v>
+        <v>0.5006784107529973</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>0.2230344616742842</v>
+        <v>0.3825533120033805</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>3.411615</v>
+        <v>3.242</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>0.10552</v>
+        <v>0.090465</v>
       </c>
       <c r="H35" s="11" t="n">
-        <v>0.240675</v>
+        <v>0.23644</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>0.38996</v>
+        <v>0.3713</v>
       </c>
       <c r="J35" s="11" t="n">
-        <v>0.263845</v>
+        <v>0.301795</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0.600125</v>
+        <v>0.56295</v>
       </c>
       <c r="L35" s="11" t="n">
-        <v>0.19078</v>
+        <v>0.2214</v>
       </c>
       <c r="M35" s="11" t="n">
-        <v>0.056055</v>
+        <v>0.066965</v>
       </c>
       <c r="N35" s="11" t="n">
-        <v>0.017065</v>
+        <v>0.015165</v>
       </c>
       <c r="O35" s="11" t="n">
-        <v>0.00482</v>
+        <v>0.00349</v>
       </c>
       <c r="P35" s="11" t="n">
-        <v>0.001215</v>
+        <v>0.000655</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>1802</v>
+        <v>1764</v>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.4530157252891658</v>
+        <v>0.2143576399911897</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>0.2707032141158732</v>
+        <v>0.7532124286596525</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>3.334235</v>
+        <v>2.504125</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>0.10511</v>
+        <v>0.05631</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>0.248165</v>
+        <v>0.14429</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0.346295</v>
+        <v>0.32196</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>0.30043</v>
+        <v>0.47744</v>
       </c>
       <c r="K36" s="8" t="n">
-        <v>0.57441</v>
+        <v>0.39284</v>
       </c>
       <c r="L36" s="8" t="n">
-        <v>0.2296</v>
+        <v>0.125255</v>
       </c>
       <c r="M36" s="8" t="n">
-        <v>0.07217999999999999</v>
+        <v>0.03405</v>
       </c>
       <c r="N36" s="8" t="n">
-        <v>0.018395</v>
+        <v>0.009639999999999999</v>
       </c>
       <c r="O36" s="8" t="n">
-        <v>0.004795</v>
+        <v>0.00238</v>
       </c>
       <c r="P36" s="8" t="n">
-        <v>0.001095</v>
+        <v>0.00059</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
@@ -6604,154 +7336,154 @@
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>1739</v>
+        <v>1771</v>
       </c>
       <c r="D37" s="12" t="n">
-        <v>0.2701988021682375</v>
+        <v>0.6132806155904944</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>0.5029250636984586</v>
+        <v>0.3085057820138778</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>2.71299</v>
+        <v>2.777275</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>0.06726500000000001</v>
+        <v>0.07525</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>0.163335</v>
+        <v>0.16562</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>0.344435</v>
+        <v>0.33911</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>0.424965</v>
+        <v>0.42002</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0.44093</v>
+        <v>0.453375</v>
       </c>
       <c r="L37" s="11" t="n">
-        <v>0.113795</v>
+        <v>0.11427</v>
       </c>
       <c r="M37" s="11" t="n">
-        <v>0.03513</v>
+        <v>0.03524</v>
       </c>
       <c r="N37" s="11" t="n">
-        <v>0.00988</v>
+        <v>0.009475000000000001</v>
       </c>
       <c r="O37" s="11" t="n">
-        <v>0.00246</v>
+        <v>0.002195</v>
       </c>
       <c r="P37" s="11" t="n">
-        <v>0.00053</v>
+        <v>0.000495</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C38" s="7" t="n">
-        <v>1732</v>
+        <v>1739</v>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.4367054341397828</v>
+        <v>0.318283565464682</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>0.325692037266015</v>
+        <v>0.6407257209349603</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>2.78387</v>
+        <v>2.68048</v>
       </c>
       <c r="G38" s="8" t="n">
-        <v>0.094045</v>
+        <v>0.067445</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>0.168755</v>
+        <v>0.16104</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0.274045</v>
+        <v>0.33392</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>0.463155</v>
+        <v>0.437595</v>
       </c>
       <c r="K38" s="8" t="n">
-        <v>0.44143</v>
+        <v>0.434595</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>0.14345</v>
+        <v>0.108265</v>
       </c>
       <c r="M38" s="8" t="n">
-        <v>0.037615</v>
+        <v>0.032695</v>
       </c>
       <c r="N38" s="8" t="n">
-        <v>0.008670000000000001</v>
+        <v>0.008965000000000001</v>
       </c>
       <c r="O38" s="8" t="n">
-        <v>0.00211</v>
+        <v>0.00202</v>
       </c>
       <c r="P38" s="8" t="n">
-        <v>0.000525</v>
+        <v>0.00039</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>1771</v>
+        <v>1732</v>
       </c>
       <c r="D39" s="12" t="n">
-        <v>0.5475481668120674</v>
+        <v>0.4775985172044392</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>0.1391259961320378</v>
+        <v>0.436869389255715</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>2.67271</v>
+        <v>2.783335</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>0.06728000000000001</v>
+        <v>0.092415</v>
       </c>
       <c r="H39" s="11" t="n">
-        <v>0.15728</v>
+        <v>0.169665</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>0.335625</v>
+        <v>0.278045</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>0.439815</v>
+        <v>0.459875</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0.42766</v>
+        <v>0.44493</v>
       </c>
       <c r="L39" s="11" t="n">
-        <v>0.104945</v>
+        <v>0.143005</v>
       </c>
       <c r="M39" s="11" t="n">
-        <v>0.031485</v>
+        <v>0.03472</v>
       </c>
       <c r="N39" s="11" t="n">
-        <v>0.00856</v>
+        <v>0.007435</v>
       </c>
       <c r="O39" s="11" t="n">
-        <v>0.002045</v>
+        <v>0.0017</v>
       </c>
       <c r="P39" s="11" t="n">
-        <v>0.00046</v>
+        <v>0.000325</v>
       </c>
     </row>
     <row r="40">
@@ -6769,43 +7501,43 @@
         <v>1776</v>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.5011749040154472</v>
+        <v>0.4990840515929844</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>0.2087576968344576</v>
+        <v>0.2915143281181614</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>2.223035</v>
+        <v>2.24708</v>
       </c>
       <c r="G40" s="8" t="n">
-        <v>0.038475</v>
+        <v>0.03405</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>0.13776</v>
+        <v>0.14819</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0.271985</v>
+        <v>0.28012</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>0.55178</v>
+        <v>0.53764</v>
       </c>
       <c r="K40" s="8" t="n">
-        <v>0.329625</v>
+        <v>0.3386</v>
       </c>
       <c r="L40" s="8" t="n">
-        <v>0.08464000000000001</v>
+        <v>0.08152</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>0.02675</v>
+        <v>0.024235</v>
       </c>
       <c r="N40" s="8" t="n">
-        <v>0.006815</v>
+        <v>0.00566</v>
       </c>
       <c r="O40" s="8" t="n">
-        <v>0.001675</v>
+        <v>0.00144</v>
       </c>
       <c r="P40" s="8" t="n">
-        <v>0.00034</v>
+        <v>0.000265</v>
       </c>
     </row>
     <row r="41">
@@ -6823,43 +7555,43 @@
         <v>1738</v>
       </c>
       <c r="D41" s="12" t="n">
-        <v>0.1378661184744294</v>
+        <v>0.2028052805717956</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>0.52270014474744</v>
+        <v>0.5555153742181393</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>2.093105</v>
+        <v>2.03797</v>
       </c>
       <c r="G41" s="11" t="n">
-        <v>0.041475</v>
+        <v>0.03671</v>
       </c>
       <c r="H41" s="11" t="n">
-        <v>0.108805</v>
+        <v>0.10678</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>0.24215</v>
+        <v>0.24218</v>
       </c>
       <c r="J41" s="11" t="n">
-        <v>0.6075700000000001</v>
+        <v>0.61433</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>0.294735</v>
+        <v>0.28713</v>
       </c>
       <c r="L41" s="11" t="n">
-        <v>0.088005</v>
+        <v>0.08094</v>
       </c>
       <c r="M41" s="11" t="n">
-        <v>0.025</v>
+        <v>0.02149</v>
       </c>
       <c r="N41" s="11" t="n">
-        <v>0.006165</v>
+        <v>0.00468</v>
       </c>
       <c r="O41" s="11" t="n">
-        <v>0.00157</v>
+        <v>0.001005</v>
       </c>
       <c r="P41" s="11" t="n">
-        <v>0.00033</v>
+        <v>0.000225</v>
       </c>
     </row>
     <row r="42">
@@ -6877,43 +7609,43 @@
         <v>1693</v>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.1567617200043641</v>
+        <v>0.1936020361641129</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>0.435784043178086</v>
+        <v>0.5195534434785752</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>2.54129</v>
+        <v>2.40885</v>
       </c>
       <c r="G42" s="8" t="n">
-        <v>0.03046</v>
+        <v>0.02248</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>0.16642</v>
+        <v>0.14417</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>0.409795</v>
+        <v>0.428905</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>0.393325</v>
+        <v>0.404445</v>
       </c>
       <c r="K42" s="8" t="n">
-        <v>0.409905</v>
+        <v>0.381295</v>
       </c>
       <c r="L42" s="8" t="n">
-        <v>0.08941</v>
+        <v>0.078435</v>
       </c>
       <c r="M42" s="8" t="n">
-        <v>0.024205</v>
+        <v>0.020225</v>
       </c>
       <c r="N42" s="8" t="n">
-        <v>0.005325</v>
+        <v>0.004425</v>
       </c>
       <c r="O42" s="8" t="n">
-        <v>0.001095</v>
+        <v>0.000865</v>
       </c>
       <c r="P42" s="8" t="n">
-        <v>0.000195</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="43">
@@ -6928,46 +7660,46 @@
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>1664</v>
+        <v>1656</v>
       </c>
       <c r="D43" s="12" t="n">
-        <v>0.2025251211048442</v>
+        <v>0.2238087661408653</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>0.39541076330281</v>
+        <v>0.4583807167884121</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>2.40388</v>
+        <v>2.23383</v>
       </c>
       <c r="G43" s="11" t="n">
-        <v>0.04841</v>
+        <v>0.03827</v>
       </c>
       <c r="H43" s="11" t="n">
-        <v>0.14994</v>
+        <v>0.13239</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>0.29295</v>
+        <v>0.28811</v>
       </c>
       <c r="J43" s="11" t="n">
-        <v>0.5087</v>
+        <v>0.54123</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>0.368725</v>
+        <v>0.33383</v>
       </c>
       <c r="L43" s="11" t="n">
-        <v>0.11303</v>
+        <v>0.09844</v>
       </c>
       <c r="M43" s="11" t="n">
-        <v>0.0269</v>
+        <v>0.02132</v>
       </c>
       <c r="N43" s="11" t="n">
-        <v>0.005065</v>
+        <v>0.0035</v>
       </c>
       <c r="O43" s="11" t="n">
-        <v>0.000895</v>
+        <v>0.00061</v>
       </c>
       <c r="P43" s="11" t="n">
-        <v>0.000175</v>
+        <v>9.500000000000001e-05</v>
       </c>
     </row>
     <row r="44">
@@ -6982,259 +7714,259 @@
         </is>
       </c>
       <c r="C44" s="7" t="n">
-        <v>1707</v>
+        <v>1689</v>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.4954254670299322</v>
+        <v>0.4921260585840237</v>
       </c>
       <c r="E44" s="9" t="n">
-        <v>0.2063251252477654</v>
+        <v>0.1892802489591522</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>2.12389</v>
+        <v>1.85667</v>
       </c>
       <c r="G44" s="8" t="n">
-        <v>0.038505</v>
+        <v>0.02621</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>0.108575</v>
+        <v>0.08584</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0.279225</v>
+        <v>0.25432</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>0.573695</v>
+        <v>0.63363</v>
       </c>
       <c r="K44" s="8" t="n">
-        <v>0.308155</v>
+        <v>0.25244</v>
       </c>
       <c r="L44" s="8" t="n">
-        <v>0.07595499999999999</v>
+        <v>0.052145</v>
       </c>
       <c r="M44" s="8" t="n">
-        <v>0.02114</v>
+        <v>0.01263</v>
       </c>
       <c r="N44" s="8" t="n">
-        <v>0.00481</v>
+        <v>0.0025</v>
       </c>
       <c r="O44" s="8" t="n">
-        <v>0.00095</v>
+        <v>0.000385</v>
       </c>
       <c r="P44" s="8" t="n">
-        <v>0.000155</v>
+        <v>5.5e-05</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>1652</v>
+        <v>1654</v>
       </c>
       <c r="D45" s="12" t="n">
-        <v>0.0937479740713611</v>
+        <v>0.1702886527719875</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>0.2159137362064919</v>
+        <v>0.3361365421806161</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>2.620735</v>
+        <v>1.98059</v>
       </c>
       <c r="G45" s="11" t="n">
-        <v>0.040515</v>
+        <v>0.013385</v>
       </c>
       <c r="H45" s="11" t="n">
-        <v>0.13944</v>
+        <v>0.10104</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>0.45158</v>
+        <v>0.35515</v>
       </c>
       <c r="J45" s="11" t="n">
-        <v>0.368465</v>
+        <v>0.530425</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>0.4309</v>
+        <v>0.27657</v>
       </c>
       <c r="L45" s="11" t="n">
-        <v>0.10658</v>
+        <v>0.046175</v>
       </c>
       <c r="M45" s="11" t="n">
-        <v>0.022235</v>
+        <v>0.009535</v>
       </c>
       <c r="N45" s="11" t="n">
-        <v>0.003065</v>
+        <v>0.0017</v>
       </c>
       <c r="O45" s="11" t="n">
-        <v>0.000525</v>
+        <v>0.000225</v>
       </c>
       <c r="P45" s="11" t="n">
-        <v>5e-05</v>
+        <v>4e-05</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C46" s="7" t="n">
-        <v>1654</v>
+        <v>1675</v>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.1636124016190125</v>
+        <v>0.1097211177761852</v>
       </c>
       <c r="E46" s="9" t="n">
-        <v>0.2366690117657277</v>
+        <v>0.247061144330814</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>2.090865</v>
+        <v>2.61844</v>
       </c>
       <c r="G46" s="8" t="n">
-        <v>0.01894</v>
+        <v>0.044525</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>0.118285</v>
+        <v>0.145135</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0.341345</v>
+        <v>0.422175</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>0.5214299999999999</v>
+        <v>0.388165</v>
       </c>
       <c r="K46" s="8" t="n">
-        <v>0.29881</v>
+        <v>0.432825</v>
       </c>
       <c r="L46" s="8" t="n">
-        <v>0.053215</v>
+        <v>0.10412</v>
       </c>
       <c r="M46" s="8" t="n">
-        <v>0.011905</v>
+        <v>0.021785</v>
       </c>
       <c r="N46" s="8" t="n">
-        <v>0.00216</v>
+        <v>0.002785</v>
       </c>
       <c r="O46" s="8" t="n">
-        <v>0.000385</v>
+        <v>0.00039</v>
       </c>
       <c r="P46" s="8" t="n">
-        <v>3.5e-05</v>
+        <v>2e-05</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1626</v>
+        <v>1591</v>
       </c>
       <c r="D47" s="12" t="n">
-        <v>0.2091129233441082</v>
+        <v>0.2965735534823266</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>0.2933588797228135</v>
+        <v>0.0914678671929548</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>1.968</v>
+        <v>2.08199</v>
       </c>
       <c r="G47" s="11" t="n">
-        <v>0.02844</v>
+        <v>0.02691</v>
       </c>
       <c r="H47" s="11" t="n">
-        <v>0.101005</v>
+        <v>0.09805</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>0.264835</v>
+        <v>0.33591</v>
       </c>
       <c r="J47" s="11" t="n">
-        <v>0.60572</v>
+        <v>0.53913</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>0.275835</v>
+        <v>0.300605</v>
       </c>
       <c r="L47" s="11" t="n">
-        <v>0.052745</v>
+        <v>0.05709</v>
       </c>
       <c r="M47" s="11" t="n">
-        <v>0.0098</v>
+        <v>0.00944</v>
       </c>
       <c r="N47" s="11" t="n">
-        <v>0.001795</v>
+        <v>0.00098</v>
       </c>
       <c r="O47" s="11" t="n">
-        <v>0.00034</v>
+        <v>0.00012</v>
       </c>
       <c r="P47" s="11" t="n">
-        <v>3.5e-05</v>
+        <v>2e-05</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C48" s="7" t="n">
-        <v>1606</v>
+        <v>1626</v>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.1983495525300176</v>
+        <v>0.2470575427398329</v>
       </c>
       <c r="E48" s="9" t="n">
-        <v>0.1095135590336114</v>
+        <v>0.3542041018361659</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>1.580635</v>
+        <v>1.794485</v>
       </c>
       <c r="G48" s="8" t="n">
-        <v>0.02023</v>
+        <v>0.021515</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>0.063365</v>
+        <v>0.08628</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.19799</v>
+        <v>0.2496</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>0.718415</v>
+        <v>0.642605</v>
       </c>
       <c r="K48" s="8" t="n">
-        <v>0.19019</v>
+        <v>0.240805</v>
       </c>
       <c r="L48" s="8" t="n">
-        <v>0.03266</v>
+        <v>0.04064</v>
       </c>
       <c r="M48" s="8" t="n">
-        <v>0.00538</v>
+        <v>0.007095</v>
       </c>
       <c r="N48" s="8" t="n">
-        <v>0.000775</v>
+        <v>0.00112</v>
       </c>
       <c r="O48" s="8" t="n">
-        <v>0.00012</v>
+        <v>0.00022</v>
       </c>
       <c r="P48" s="8" t="n">
         <v>2e-05</v>
@@ -7243,55 +7975,55 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>1566</v>
+        <v>1606</v>
       </c>
       <c r="D49" s="12" t="n">
-        <v>0.153897955524102</v>
+        <v>0.1699041265493231</v>
       </c>
       <c r="E49" s="12" t="n">
-        <v>-0.0068485106014388</v>
+        <v>0.1399842928429243</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>1.907965</v>
+        <v>1.47832</v>
       </c>
       <c r="G49" s="11" t="n">
-        <v>0.019715</v>
+        <v>0.01573</v>
       </c>
       <c r="H49" s="11" t="n">
-        <v>0.08057</v>
+        <v>0.055205</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>0.326335</v>
+        <v>0.194495</v>
       </c>
       <c r="J49" s="11" t="n">
-        <v>0.57338</v>
+        <v>0.7345699999999999</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>0.25895</v>
+        <v>0.17337</v>
       </c>
       <c r="L49" s="11" t="n">
-        <v>0.046745</v>
+        <v>0.026395</v>
       </c>
       <c r="M49" s="11" t="n">
-        <v>0.007</v>
+        <v>0.003975</v>
       </c>
       <c r="N49" s="11" t="n">
-        <v>0.000705</v>
+        <v>0.000495</v>
       </c>
       <c r="O49" s="11" t="n">
-        <v>6.499999999999999e-05</v>
+        <v>7.499999999999999e-05</v>
       </c>
       <c r="P49" s="11" t="n">
-        <v>0</v>
+        <v>5e-06</v>
       </c>
     </row>
   </sheetData>
@@ -7374,25 +8106,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1980</v>
+        <v>1988</v>
       </c>
       <c r="C3" s="14" t="n">
-        <v>6.406305</v>
+        <v>6.493745</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.636405</v>
+        <v>0.64407</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>0.23722</v>
+        <v>0.239615</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0.093835</v>
+        <v>0.08903999999999999</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.03254</v>
+        <v>0.027275</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.952385</v>
+        <v>0.95903</v>
       </c>
     </row>
     <row r="4">
@@ -7402,25 +8134,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1881</v>
+        <v>1904</v>
       </c>
       <c r="C4" s="14" t="n">
-        <v>4.368295</v>
+        <v>4.582255</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.210075</v>
+        <v>0.227195</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0.364675</v>
+        <v>0.391555</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.26692</v>
+        <v>0.25155</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.15833</v>
+        <v>0.1297</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.76208</v>
+        <v>0.79945</v>
       </c>
     </row>
     <row r="5">
@@ -7430,25 +8162,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1802</v>
+        <v>1779</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>3.334235</v>
+        <v>3.242</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.10511</v>
+        <v>0.090465</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>0.248165</v>
+        <v>0.23644</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.346295</v>
+        <v>0.3713</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.30043</v>
+        <v>0.301795</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.57441</v>
+        <v>0.56295</v>
       </c>
     </row>
     <row r="6">
@@ -7458,25 +8190,25 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1664</v>
+        <v>1656</v>
       </c>
       <c r="C6" s="14" t="n">
-        <v>2.40388</v>
+        <v>2.23383</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.04841</v>
+        <v>0.03827</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0.14994</v>
+        <v>0.13239</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.29295</v>
+        <v>0.28811</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.5087</v>
+        <v>0.54123</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.368725</v>
+        <v>0.33383</v>
       </c>
     </row>
     <row r="8">
@@ -7535,25 +8267,25 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1899</v>
+        <v>1876</v>
       </c>
       <c r="C10" s="14" t="n">
-        <v>6.28332</v>
+        <v>6.248805</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.51856</v>
+        <v>0.52981</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>0.361005</v>
+        <v>0.341055</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.096895</v>
+        <v>0.101385</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.02354</v>
+        <v>0.02775</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.958425</v>
+        <v>0.953965</v>
       </c>
     </row>
     <row r="11">
@@ -7563,25 +8295,25 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1956</v>
+        <v>1932</v>
       </c>
       <c r="C11" s="14" t="n">
-        <v>5.890855</v>
+        <v>5.723065</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0.42121</v>
+        <v>0.398755</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>0.418985</v>
+        <v>0.41576</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0.12519</v>
+        <v>0.14053</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.034615</v>
+        <v>0.044955</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.93916</v>
+        <v>0.924775</v>
       </c>
     </row>
     <row r="12">
@@ -7591,25 +8323,25 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1652</v>
+        <v>1675</v>
       </c>
       <c r="C12" s="14" t="n">
-        <v>2.620735</v>
+        <v>2.61844</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0.040515</v>
+        <v>0.044525</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>0.13944</v>
+        <v>0.145135</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.45158</v>
+        <v>0.422175</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.368465</v>
+        <v>0.388165</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.4309</v>
+        <v>0.432825</v>
       </c>
     </row>
     <row r="13">
@@ -7619,25 +8351,25 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>1566</v>
+        <v>1591</v>
       </c>
       <c r="C13" s="14" t="n">
-        <v>1.907965</v>
+        <v>2.08199</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0.019715</v>
+        <v>0.02691</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>0.08057</v>
+        <v>0.09805</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0.326335</v>
+        <v>0.33591</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.57338</v>
+        <v>0.53913</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.25895</v>
+        <v>0.300605</v>
       </c>
     </row>
     <row r="15">
@@ -7696,25 +8428,25 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>2069</v>
+        <v>2062</v>
       </c>
       <c r="C17" s="14" t="n">
-        <v>5.787515</v>
+        <v>6.041775</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0.48447</v>
+        <v>0.527195</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>0.31641</v>
+        <v>0.305855</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0.146605</v>
+        <v>0.13074</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.052515</v>
+        <v>0.03621</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.920095</v>
+        <v>0.942345</v>
       </c>
     </row>
     <row r="18">
@@ -7724,25 +8456,25 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>1985</v>
+        <v>1992</v>
       </c>
       <c r="C18" s="14" t="n">
-        <v>5.38438</v>
+        <v>5.304125</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>0.37769</v>
+        <v>0.345695</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>0.36593</v>
+        <v>0.38535</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.186495</v>
+        <v>0.201395</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.069885</v>
+        <v>0.06756</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.88822</v>
+        <v>0.88761</v>
       </c>
     </row>
     <row r="19">
@@ -7752,25 +8484,25 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>1844</v>
+        <v>1863</v>
       </c>
       <c r="C19" s="14" t="n">
-        <v>3.22908</v>
+        <v>3.364055</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0.09933500000000001</v>
+        <v>0.1009</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.209085</v>
+        <v>0.222955</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.387675</v>
+        <v>0.413545</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.303905</v>
+        <v>0.2626</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.56069</v>
+        <v>0.59748</v>
       </c>
     </row>
     <row r="20">
@@ -7780,25 +8512,25 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1707</v>
+        <v>1689</v>
       </c>
       <c r="C20" s="14" t="n">
-        <v>2.12389</v>
+        <v>1.85667</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>0.038505</v>
+        <v>0.02621</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0.108575</v>
+        <v>0.08584</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0.279225</v>
+        <v>0.25432</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.573695</v>
+        <v>0.63363</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.308155</v>
+        <v>0.25244</v>
       </c>
     </row>
     <row r="22">
@@ -7853,85 +8585,85 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>1969</v>
+        <v>1878</v>
       </c>
       <c r="C24" s="14" t="n">
-        <v>4.19187</v>
+        <v>4.674895</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0.270185</v>
+        <v>0.34216</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>0.252295</v>
+        <v>0.27167</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.243925</v>
+        <v>0.21715</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.233595</v>
+        <v>0.16902</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.705095</v>
+        <v>0.781875</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1827</v>
+        <v>1956</v>
       </c>
       <c r="C25" s="14" t="n">
-        <v>4.12912</v>
+        <v>4.456375</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0.263025</v>
+        <v>0.29885</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>0.250985</v>
+        <v>0.27369</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>0.242785</v>
+        <v>0.23667</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.243205</v>
+        <v>0.19079</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.69607</v>
+        <v>0.752115</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>1902</v>
+        <v>1916</v>
       </c>
       <c r="C26" s="14" t="n">
-        <v>4.115365</v>
+        <v>3.741415</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>0.253215</v>
+        <v>0.20004</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>0.254845</v>
+        <v>0.23649</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>0.250745</v>
+        <v>0.26932</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.241195</v>
+        <v>0.29415</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.69434</v>
+        <v>0.6322950000000001</v>
       </c>
     </row>
     <row r="27">
@@ -7941,25 +8673,25 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>1919</v>
+        <v>1867</v>
       </c>
       <c r="C27" s="14" t="n">
-        <v>3.84315</v>
+        <v>3.424235</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>0.213575</v>
+        <v>0.15895</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>0.241875</v>
+        <v>0.21815</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>0.262545</v>
+        <v>0.27686</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.282005</v>
+        <v>0.34604</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.64677</v>
+        <v>0.573105</v>
       </c>
     </row>
     <row r="29">
@@ -8021,22 +8753,22 @@
         <v>2005</v>
       </c>
       <c r="C31" s="14" t="n">
-        <v>5.52947</v>
+        <v>5.664715</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>0.427675</v>
+        <v>0.434815</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>0.325185</v>
+        <v>0.339145</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>0.19431</v>
+        <v>0.183095</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.05283</v>
+        <v>0.042945</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.912025</v>
+        <v>0.925235</v>
       </c>
     </row>
     <row r="32">
@@ -8049,22 +8781,22 @@
         <v>2028</v>
       </c>
       <c r="C32" s="14" t="n">
-        <v>5.45213</v>
+        <v>5.6244</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>0.394425</v>
+        <v>0.41523</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>0.34455</v>
+        <v>0.351095</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0.204865</v>
+        <v>0.188225</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.05616</v>
+        <v>0.04545</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.90101</v>
+        <v>0.91854</v>
       </c>
     </row>
     <row r="33">
@@ -8077,22 +8809,22 @@
         <v>1816</v>
       </c>
       <c r="C33" s="14" t="n">
-        <v>3.921595</v>
+        <v>3.79397</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>0.15767</v>
+        <v>0.134225</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>0.2669</v>
+        <v>0.254555</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>0.402835</v>
+        <v>0.434185</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.172595</v>
+        <v>0.177035</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0.708345</v>
+        <v>0.692145</v>
       </c>
     </row>
     <row r="34">
@@ -8105,22 +8837,22 @@
         <v>1606</v>
       </c>
       <c r="C34" s="14" t="n">
-        <v>1.580635</v>
+        <v>1.47832</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>0.02023</v>
+        <v>0.01573</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>0.063365</v>
+        <v>0.055205</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>0.19799</v>
+        <v>0.194495</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.718415</v>
+        <v>0.7345699999999999</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.19019</v>
+        <v>0.17337</v>
       </c>
     </row>
     <row r="36">
@@ -8182,22 +8914,22 @@
         <v>1994</v>
       </c>
       <c r="C38" s="14" t="n">
-        <v>5.679635</v>
+        <v>5.53836</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>0.456665</v>
+        <v>0.432265</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>0.330495</v>
+        <v>0.33571</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>0.151665</v>
+        <v>0.162575</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0.061175</v>
+        <v>0.06945</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>0.907695</v>
+        <v>0.89695</v>
       </c>
     </row>
     <row r="39">
@@ -8210,78 +8942,78 @@
         <v>2011</v>
       </c>
       <c r="C39" s="14" t="n">
-        <v>5.453395</v>
+        <v>5.497355</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>0.40879</v>
+        <v>0.42504</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>0.34889</v>
+        <v>0.33763</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.168275</v>
+        <v>0.164395</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0.074045</v>
+        <v>0.072935</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>0.888825</v>
+        <v>0.892285</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>1739</v>
+        <v>1771</v>
       </c>
       <c r="C40" s="14" t="n">
-        <v>2.71299</v>
+        <v>2.777275</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>0.06726500000000001</v>
+        <v>0.07525</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>0.163335</v>
+        <v>0.16562</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.344435</v>
+        <v>0.33911</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0.424965</v>
+        <v>0.42002</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>0.44093</v>
+        <v>0.453375</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>1771</v>
+        <v>1739</v>
       </c>
       <c r="C41" s="14" t="n">
-        <v>2.67271</v>
+        <v>2.68048</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>0.06728000000000001</v>
+        <v>0.067445</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>0.15728</v>
+        <v>0.16104</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>0.335625</v>
+        <v>0.33392</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0.439815</v>
+        <v>0.437595</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>0.42766</v>
+        <v>0.434595</v>
       </c>
     </row>
     <row r="43">
@@ -8343,22 +9075,22 @@
         <v>1957</v>
       </c>
       <c r="C45" s="14" t="n">
-        <v>5.233945</v>
+        <v>5.33011</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>0.42708</v>
+        <v>0.443335</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>0.282415</v>
+        <v>0.28247</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>0.184435</v>
+        <v>0.176365</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>0.10607</v>
+        <v>0.09783</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>0.85544</v>
+        <v>0.866885</v>
       </c>
     </row>
     <row r="46">
@@ -8371,22 +9103,22 @@
         <v>1897</v>
       </c>
       <c r="C46" s="14" t="n">
-        <v>4.63744</v>
+        <v>4.610695</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>0.31062</v>
+        <v>0.302935</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>0.298365</v>
+        <v>0.302045</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>0.235155</v>
+        <v>0.237675</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0.15586</v>
+        <v>0.157345</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>0.7852</v>
+        <v>0.784325</v>
       </c>
     </row>
     <row r="47">
@@ -8399,22 +9131,22 @@
         <v>1811</v>
       </c>
       <c r="C47" s="14" t="n">
-        <v>3.678295</v>
+        <v>3.61768</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>0.168255</v>
+        <v>0.161315</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>0.250465</v>
+        <v>0.24582</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.306365</v>
+        <v>0.307915</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0.274915</v>
+        <v>0.28495</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>0.631515</v>
+        <v>0.62273</v>
       </c>
     </row>
     <row r="48">
@@ -8427,22 +9159,22 @@
         <v>1732</v>
       </c>
       <c r="C48" s="14" t="n">
-        <v>2.78387</v>
+        <v>2.783335</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>0.094045</v>
+        <v>0.092415</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>0.168755</v>
+        <v>0.169665</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.274045</v>
+        <v>0.278045</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0.463155</v>
+        <v>0.459875</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>0.44143</v>
+        <v>0.44493</v>
       </c>
     </row>
     <row r="50">
@@ -8504,22 +9236,22 @@
         <v>2219</v>
       </c>
       <c r="C52" s="14" t="n">
-        <v>7.129455</v>
+        <v>7.246165</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>0.75073</v>
+        <v>0.75499</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>0.200035</v>
+        <v>0.20556</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0.040875</v>
+        <v>0.033635</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>0.008359999999999999</v>
+        <v>0.005815</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>0.98625</v>
+        <v>0.990035</v>
       </c>
     </row>
     <row r="53">
@@ -8532,22 +9264,22 @@
         <v>1976</v>
       </c>
       <c r="C53" s="14" t="n">
-        <v>4.885175</v>
+        <v>5.09071</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>0.19987</v>
+        <v>0.209145</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>0.5152600000000001</v>
+        <v>0.54923</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>0.207985</v>
+        <v>0.18231</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>0.076885</v>
+        <v>0.059315</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>0.85407</v>
+        <v>0.88295</v>
       </c>
     </row>
     <row r="54">
@@ -8560,22 +9292,22 @@
         <v>1693</v>
       </c>
       <c r="C54" s="14" t="n">
-        <v>2.54129</v>
+        <v>2.40885</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>0.03046</v>
+        <v>0.02248</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>0.16642</v>
+        <v>0.14417</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>0.409795</v>
+        <v>0.428905</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>0.393325</v>
+        <v>0.404445</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>0.409905</v>
+        <v>0.381295</v>
       </c>
     </row>
     <row r="55">
@@ -8588,22 +9320,22 @@
         <v>1654</v>
       </c>
       <c r="C55" s="14" t="n">
-        <v>2.090865</v>
+        <v>1.98059</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>0.01894</v>
+        <v>0.013385</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>0.118285</v>
+        <v>0.10104</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>0.341345</v>
+        <v>0.35515</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>0.5214299999999999</v>
+        <v>0.530425</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>0.29881</v>
+        <v>0.27657</v>
       </c>
     </row>
     <row r="57">
@@ -8665,22 +9397,22 @@
         <v>2125</v>
       </c>
       <c r="C59" s="14" t="n">
-        <v>5.61503</v>
+        <v>5.92685</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>0.475935</v>
+        <v>0.536545</v>
       </c>
       <c r="E59" s="6" t="n">
-        <v>0.286125</v>
+        <v>0.2725</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>0.17159</v>
+        <v>0.142185</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>0.06635000000000001</v>
+        <v>0.04877</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>0.8995300000000001</v>
+        <v>0.926215</v>
       </c>
     </row>
     <row r="60">
@@ -8693,22 +9425,22 @@
         <v>1972</v>
       </c>
       <c r="C60" s="14" t="n">
-        <v>4.579885</v>
+        <v>4.464975</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>0.27396</v>
+        <v>0.243875</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>0.314785</v>
+        <v>0.32653</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>0.26965</v>
+        <v>0.28316</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>0.141605</v>
+        <v>0.146435</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>0.78822</v>
+        <v>0.77888</v>
       </c>
     </row>
     <row r="61">
@@ -8721,22 +9453,22 @@
         <v>1914</v>
       </c>
       <c r="C61" s="14" t="n">
-        <v>4.14828</v>
+        <v>4.035415</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>0.20863</v>
+        <v>0.18287</v>
       </c>
       <c r="E61" s="6" t="n">
-        <v>0.290285</v>
+        <v>0.29419</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>0.31661</v>
+        <v>0.332475</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>0.184475</v>
+        <v>0.190465</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>0.7248</v>
+        <v>0.7125899999999999</v>
       </c>
     </row>
     <row r="62">
@@ -8749,22 +9481,22 @@
         <v>1738</v>
       </c>
       <c r="C62" s="14" t="n">
-        <v>2.093105</v>
+        <v>2.03797</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>0.041475</v>
+        <v>0.03671</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>0.108805</v>
+        <v>0.10678</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>0.24215</v>
+        <v>0.24218</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>0.6075700000000001</v>
+        <v>0.61433</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>0.294735</v>
+        <v>0.28713</v>
       </c>
     </row>
     <row r="64">
@@ -8826,22 +9558,22 @@
         <v>2190</v>
       </c>
       <c r="C66" s="14" t="n">
-        <v>6.649965</v>
+        <v>6.89114</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>0.68873</v>
+        <v>0.734545</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>0.21043</v>
+        <v>0.18664</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>0.078305</v>
+        <v>0.061565</v>
       </c>
       <c r="G66" s="6" t="n">
-        <v>0.022535</v>
+        <v>0.01725</v>
       </c>
       <c r="H66" s="6" t="n">
-        <v>0.96623</v>
+        <v>0.974945</v>
       </c>
     </row>
     <row r="67">
@@ -8854,22 +9586,22 @@
         <v>1885</v>
       </c>
       <c r="C67" s="14" t="n">
-        <v>4.026315</v>
+        <v>3.821605</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>0.15529</v>
+        <v>0.12454</v>
       </c>
       <c r="E67" s="6" t="n">
-        <v>0.35139</v>
+        <v>0.3469</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>0.30644</v>
+        <v>0.319185</v>
       </c>
       <c r="G67" s="6" t="n">
-        <v>0.18688</v>
+        <v>0.209375</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>0.714995</v>
+        <v>0.683285</v>
       </c>
     </row>
     <row r="68">
@@ -8882,22 +9614,22 @@
         <v>1890</v>
       </c>
       <c r="C68" s="14" t="n">
-        <v>3.638135</v>
+        <v>3.6255</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>0.117505</v>
+        <v>0.106865</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>0.30042</v>
+        <v>0.31827</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>0.34327</v>
+        <v>0.33913</v>
       </c>
       <c r="G68" s="6" t="n">
-        <v>0.238805</v>
+        <v>0.235735</v>
       </c>
       <c r="H68" s="6" t="n">
-        <v>0.64462</v>
+        <v>0.64506</v>
       </c>
     </row>
     <row r="69">
@@ -8910,22 +9642,22 @@
         <v>1776</v>
       </c>
       <c r="C69" s="14" t="n">
-        <v>2.223035</v>
+        <v>2.24708</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>0.038475</v>
+        <v>0.03405</v>
       </c>
       <c r="E69" s="6" t="n">
-        <v>0.13776</v>
+        <v>0.14819</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>0.271985</v>
+        <v>0.28012</v>
       </c>
       <c r="G69" s="6" t="n">
-        <v>0.55178</v>
+        <v>0.53764</v>
       </c>
       <c r="H69" s="6" t="n">
-        <v>0.329625</v>
+        <v>0.3386</v>
       </c>
     </row>
     <row r="71">
@@ -8987,22 +9719,22 @@
         <v>2064</v>
       </c>
       <c r="C73" s="14" t="n">
-        <v>5.423645</v>
+        <v>5.599005</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>0.43724</v>
+        <v>0.45401</v>
       </c>
       <c r="E73" s="6" t="n">
-        <v>0.315905</v>
+        <v>0.32813</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>0.165965</v>
+        <v>0.15252</v>
       </c>
       <c r="G73" s="6" t="n">
-        <v>0.08089</v>
+        <v>0.06534</v>
       </c>
       <c r="H73" s="6" t="n">
-        <v>0.881905</v>
+        <v>0.9020049999999999</v>
       </c>
     </row>
     <row r="74">
@@ -9015,22 +9747,22 @@
         <v>2046</v>
       </c>
       <c r="C74" s="14" t="n">
-        <v>5.257015</v>
+        <v>5.41159</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>0.399095</v>
+        <v>0.409065</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>0.32951</v>
+        <v>0.34553</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>0.18044</v>
+        <v>0.169395</v>
       </c>
       <c r="G74" s="6" t="n">
-        <v>0.09095499999999999</v>
+        <v>0.07600999999999999</v>
       </c>
       <c r="H74" s="6" t="n">
-        <v>0.866645</v>
+        <v>0.88626</v>
       </c>
     </row>
     <row r="75">
@@ -9043,22 +9775,22 @@
         <v>1821</v>
       </c>
       <c r="C75" s="14" t="n">
-        <v>2.89785</v>
+        <v>2.908125</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>0.086475</v>
+        <v>0.08061500000000001</v>
       </c>
       <c r="E75" s="6" t="n">
-        <v>0.183175</v>
+        <v>0.18205</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>0.329085</v>
+        <v>0.356125</v>
       </c>
       <c r="G75" s="6" t="n">
-        <v>0.401265</v>
+        <v>0.38121</v>
       </c>
       <c r="H75" s="6" t="n">
-        <v>0.472385</v>
+        <v>0.48315</v>
       </c>
     </row>
     <row r="76">
@@ -9071,22 +9803,22 @@
         <v>1764</v>
       </c>
       <c r="C76" s="14" t="n">
-        <v>2.77356</v>
+        <v>2.504125</v>
       </c>
       <c r="D76" s="6" t="n">
-        <v>0.07718999999999999</v>
+        <v>0.05631</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>0.17141</v>
+        <v>0.14429</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>0.32451</v>
+        <v>0.32196</v>
       </c>
       <c r="G76" s="6" t="n">
-        <v>0.42689</v>
+        <v>0.47744</v>
       </c>
       <c r="H76" s="6" t="n">
-        <v>0.44694</v>
+        <v>0.39284</v>
       </c>
     </row>
     <row r="78">
@@ -9148,22 +9880,22 @@
         <v>2091</v>
       </c>
       <c r="C80" s="14" t="n">
-        <v>6.33173</v>
+        <v>6.431035</v>
       </c>
       <c r="D80" s="6" t="n">
-        <v>0.5989449999999999</v>
+        <v>0.608995</v>
       </c>
       <c r="E80" s="6" t="n">
-        <v>0.26728</v>
+        <v>0.267785</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>0.10409</v>
+        <v>0.099435</v>
       </c>
       <c r="G80" s="6" t="n">
-        <v>0.029685</v>
+        <v>0.023785</v>
       </c>
       <c r="H80" s="6" t="n">
-        <v>0.9537</v>
+        <v>0.9614</v>
       </c>
     </row>
     <row r="81">
@@ -9176,22 +9908,22 @@
         <v>1969</v>
       </c>
       <c r="C81" s="14" t="n">
-        <v>4.842275</v>
+        <v>4.95143</v>
       </c>
       <c r="D81" s="6" t="n">
-        <v>0.267095</v>
+        <v>0.27021</v>
       </c>
       <c r="E81" s="6" t="n">
-        <v>0.39104</v>
+        <v>0.40699</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>0.241115</v>
+        <v>0.236465</v>
       </c>
       <c r="G81" s="6" t="n">
-        <v>0.10075</v>
+        <v>0.086335</v>
       </c>
       <c r="H81" s="6" t="n">
-        <v>0.83594</v>
+        <v>0.854325</v>
       </c>
     </row>
     <row r="82">
@@ -9204,22 +9936,22 @@
         <v>1854</v>
       </c>
       <c r="C82" s="14" t="n">
-        <v>3.411615</v>
+        <v>3.422615</v>
       </c>
       <c r="D82" s="6" t="n">
-        <v>0.10552</v>
+        <v>0.09927999999999999</v>
       </c>
       <c r="E82" s="6" t="n">
-        <v>0.240675</v>
+        <v>0.238945</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>0.38996</v>
+        <v>0.4145</v>
       </c>
       <c r="G82" s="6" t="n">
-        <v>0.263845</v>
+        <v>0.247275</v>
       </c>
       <c r="H82" s="6" t="n">
-        <v>0.600125</v>
+        <v>0.6096</v>
       </c>
     </row>
     <row r="83">
@@ -9232,22 +9964,22 @@
         <v>1626</v>
       </c>
       <c r="C83" s="14" t="n">
-        <v>1.968</v>
+        <v>1.794485</v>
       </c>
       <c r="D83" s="6" t="n">
-        <v>0.02844</v>
+        <v>0.021515</v>
       </c>
       <c r="E83" s="6" t="n">
-        <v>0.101005</v>
+        <v>0.08628</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>0.264835</v>
+        <v>0.2496</v>
       </c>
       <c r="G83" s="6" t="n">
-        <v>0.60572</v>
+        <v>0.642605</v>
       </c>
       <c r="H83" s="6" t="n">
-        <v>0.275835</v>
+        <v>0.240805</v>
       </c>
     </row>
   </sheetData>
@@ -9324,10 +10056,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.9255</v>
+        <v>0.9247</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.5467</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>48</v>
@@ -9345,10 +10077,10 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.9376</v>
+        <v>0.9482</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.5548</v>
+        <v>0.5625</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>48</v>
@@ -9366,10 +10098,10 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.9246</v>
+        <v>0.9172</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.5468</v>
+        <v>0.5414</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>48</v>
@@ -9408,10 +10140,10 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.9510999999999999</v>
+        <v>0.961</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.5619</v>
+        <v>0.5696</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>48</v>
@@ -9429,10 +10161,10 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.9516</v>
+        <v>0.9547</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.5646</v>
+        <v>0.5678</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>48</v>
@@ -9450,10 +10182,10 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.9638</v>
+        <v>0.9741</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.5682</v>
+        <v>0.5767</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>48</v>
@@ -9492,10 +10224,10 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>1.0776</v>
+        <v>1.0946</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.6355</v>
+        <v>0.6398</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>48</v>
@@ -9513,10 +10245,10 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1.0791</v>
+        <v>1.0746</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.641</v>
+        <v>0.633</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>48</v>
@@ -9534,10 +10266,10 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1.1017</v>
+        <v>1.1244</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.6429</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>48</v>
@@ -9572,7 +10304,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>time decay xi = 0.7/yr, friendly weight = 0.7, blend weight = 0.5</t>
+          <t>time decay xi = 0.4/yr, friendly weight = 0.7, blend weight = 0.4</t>
         </is>
       </c>
     </row>
